--- a/output/yearly_surface_area_iteration_78_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_78_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497646061877</v>
+        <v>10.84497639959285</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907238932929</v>
+        <v>37.78907217668586</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.566910393706914</v>
+        <v>5.687264450701772</v>
       </c>
       <c r="C2" t="n">
-        <v>7.355253800217104</v>
+        <v>9.86165568915921</v>
       </c>
       <c r="D2" t="n">
-        <v>23.2399316549305</v>
+        <v>40.79554410227195</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.96383956585889</v>
+        <v>18.55503161026472</v>
       </c>
       <c r="C3" t="n">
-        <v>25.49107914076843</v>
+        <v>23.95955272214341</v>
       </c>
       <c r="D3" t="n">
-        <v>65.75746123045137</v>
+        <v>86.6932310235146</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.15151760828606</v>
+        <v>36.51414236405162</v>
       </c>
       <c r="C4" t="n">
-        <v>68.0125357071063</v>
+        <v>70.71823238001049</v>
       </c>
       <c r="D4" t="n">
-        <v>82.94491828870026</v>
+        <v>114.7240914751695</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.39449231732053</v>
+        <v>43.61414176116455</v>
       </c>
       <c r="C5" t="n">
-        <v>108.5812960896972</v>
+        <v>123.4056864238241</v>
       </c>
       <c r="D5" t="n">
-        <v>62.51278506791567</v>
+        <v>83.74307917225293</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.10702016642546</v>
+        <v>41.98247707670636</v>
       </c>
       <c r="C6" t="n">
-        <v>122.2442788897001</v>
+        <v>151.0242128396953</v>
       </c>
       <c r="D6" t="n">
-        <v>43.55229165579701</v>
+        <v>51.20010627187966</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.05173919535137</v>
+        <v>30.9014907388726</v>
       </c>
       <c r="C7" t="n">
-        <v>108.4546506358494</v>
+        <v>142.3504718726747</v>
       </c>
       <c r="D7" t="n">
-        <v>38.14777054391831</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.27523351455438</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="C8" t="n">
-        <v>74.60300804571511</v>
+        <v>88.95615948180348</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.431249284071605</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>43.4874963073167</v>
+        <v>45.04062117543515</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>33.84673385161303</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>22.73924032576462</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.682104299478071</v>
+        <v>7.635262040016475</v>
       </c>
       <c r="C21" t="n">
-        <v>93.14551463117161</v>
+        <v>92.57755223519976</v>
       </c>
       <c r="D21" t="n">
-        <v>7.682104299478071</v>
+        <v>7.635262040016475</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.843182409227768</v>
+        <v>5.69708192774424</v>
       </c>
       <c r="C2" t="n">
-        <v>5.644067551714913</v>
+        <v>14.27559336745287</v>
       </c>
       <c r="D2" t="n">
-        <v>28.47559216167873</v>
+        <v>42.76002125846983</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.06339699461532</v>
+        <v>18.51085296357361</v>
       </c>
       <c r="C3" t="n">
-        <v>26.94406574305371</v>
+        <v>30.72870314292516</v>
       </c>
       <c r="D3" t="n">
-        <v>68.19710427550469</v>
+        <v>96.01492547533806</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.64551662997145</v>
+        <v>35.31444666946201</v>
       </c>
       <c r="C4" t="n">
-        <v>65.75353423963438</v>
+        <v>65.43446623575416</v>
       </c>
       <c r="D4" t="n">
-        <v>94.78872259273379</v>
+        <v>128.2270493993801</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.27239574909544</v>
+        <v>48.10563750809372</v>
       </c>
       <c r="C5" t="n">
-        <v>115.5026174046373</v>
+        <v>125.0746575210437</v>
       </c>
       <c r="D5" t="n">
-        <v>74.90734983403165</v>
+        <v>100.0891784479623</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.48565598509524</v>
+        <v>49.63029169278902</v>
       </c>
       <c r="C6" t="n">
-        <v>146.2342657906752</v>
+        <v>169.8217361329091</v>
       </c>
       <c r="D6" t="n">
-        <v>52.00513938936205</v>
+        <v>62.91333813124836</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.95110220789945</v>
+        <v>38.98618308334508</v>
       </c>
       <c r="C7" t="n">
-        <v>139.7154610344763</v>
+        <v>176.9649324290088</v>
       </c>
       <c r="D7" t="n">
-        <v>41.26187426178919</v>
+        <v>43.89688509998763</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.62147165898401</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="C8" t="n">
-        <v>107.5651872158018</v>
+        <v>131.9321652352076</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.97968639784708</v>
+        <v>11.42656152972862</v>
       </c>
       <c r="C9" t="n">
-        <v>65.89686940445439</v>
+        <v>73.66249374504666</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>34.61249706092553</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>40.71307729511523</v>
+        <v>40.00131020953629</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.0569667290421</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.861767405793516</v>
+        <v>7.801941186326613</v>
       </c>
       <c r="C21" t="n">
-        <v>101.2202553495915</v>
+        <v>100.4499927739551</v>
       </c>
       <c r="D21" t="n">
-        <v>8.844488331517704</v>
+        <v>8.777183834617439</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.484664570728436</v>
+        <v>6.884014902178635</v>
       </c>
       <c r="C2" t="n">
-        <v>13.76999329976576</v>
+        <v>13.26930197059989</v>
       </c>
       <c r="D2" t="n">
-        <v>21.92831672205676</v>
+        <v>38.24005482811751</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.04652735719387</v>
+        <v>18.22614612934204</v>
       </c>
       <c r="C3" t="n">
-        <v>24.38170423496954</v>
+        <v>41.09105016125025</v>
       </c>
       <c r="D3" t="n">
-        <v>72.73277866912495</v>
+        <v>103.2111361474672</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.46683854779853</v>
+        <v>34.20409001595887</v>
       </c>
       <c r="C4" t="n">
-        <v>65.60038159777187</v>
+        <v>69.26328228231672</v>
       </c>
       <c r="D4" t="n">
-        <v>102.880287171136</v>
+        <v>139.4071922553428</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.6222988424348</v>
+        <v>49.43099690882691</v>
       </c>
       <c r="C5" t="n">
-        <v>116.6070835719149</v>
+        <v>121.5649094783613</v>
       </c>
       <c r="D5" t="n">
-        <v>87.35100198535997</v>
+        <v>115.7725980233051</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.96617258082844</v>
+        <v>55.2252718592916</v>
       </c>
       <c r="C6" t="n">
-        <v>162.7374446990641</v>
+        <v>180.2469150043059</v>
       </c>
       <c r="D6" t="n">
-        <v>61.50453017565419</v>
+        <v>75.67311304334416</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>56.35329997147116</v>
+        <v>46.65166915810418</v>
       </c>
       <c r="C7" t="n">
-        <v>169.5389927940859</v>
+        <v>205.7703918193145</v>
       </c>
       <c r="D7" t="n">
-        <v>45.33416373900496</v>
+        <v>49.34656660626167</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>37.30150402285756</v>
+        <v>30.70906818884022</v>
       </c>
       <c r="C8" t="n">
-        <v>140.6108149407494</v>
+        <v>172.1543686781994</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.081248379741</v>
+        <v>16.19687362466387</v>
       </c>
       <c r="C9" t="n">
-        <v>95.29530440812512</v>
+        <v>108.7187407682918</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.252972112526189</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>56.08724634362028</v>
+        <v>58.64960785170445</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>38.56010457970196</v>
+        <v>36.96083756948391</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1556,10 +1556,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.13827186204534</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.025779448893564</v>
+        <v>7.952074715929364</v>
       </c>
       <c r="C21" t="n">
-        <v>109.3512449911748</v>
+        <v>107.3530086650464</v>
       </c>
       <c r="D21" t="n">
-        <v>10.03222431111695</v>
+        <v>9.940093394911704</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.579493187412876</v>
+        <v>6.384305320717008</v>
       </c>
       <c r="C2" t="n">
-        <v>9.36292785540183</v>
+        <v>9.3413294059084</v>
       </c>
       <c r="D2" t="n">
-        <v>18.10048242319844</v>
+        <v>31.7801549341735</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.3318560862312</v>
+        <v>22.38875639534851</v>
       </c>
       <c r="C3" t="n">
-        <v>41.83717841647783</v>
+        <v>57.57950285407543</v>
       </c>
       <c r="D3" t="n">
-        <v>79.18286108602649</v>
+        <v>110.1226399853647</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.19735665074939</v>
+        <v>23.73865948868787</v>
       </c>
       <c r="C4" t="n">
-        <v>94.72490899195775</v>
+        <v>96.58826613461819</v>
       </c>
       <c r="D4" t="n">
-        <v>98.55372503852031</v>
+        <v>131.8516619234594</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.59464567579986</v>
+        <v>31.09685853201772</v>
       </c>
       <c r="C5" t="n">
-        <v>97.24211010564659</v>
+        <v>107.6977231558751</v>
       </c>
       <c r="D5" t="n">
-        <v>60.23022165554183</v>
+        <v>75.22641783791185</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.97868895460962</v>
+        <v>28.94094057349173</v>
       </c>
       <c r="C6" t="n">
-        <v>111.6580933948068</v>
+        <v>135.5273253281594</v>
       </c>
       <c r="D6" t="n">
-        <v>29.82647700272235</v>
+        <v>32.48308629041422</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.73316991308989</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="C7" t="n">
-        <v>98.87279304240052</v>
+        <v>121.030838727251</v>
       </c>
       <c r="D7" t="n">
-        <v>28.26647990067416</v>
+        <v>28.20659329071511</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.18487166803466</v>
+        <v>11.18210635137117</v>
       </c>
       <c r="C8" t="n">
-        <v>70.18023463808323</v>
+        <v>80.11061266653972</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>26.20284622634736</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>42.82187136383736</v>
+        <v>44.70780870369548</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>28.89774367450487</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>25.58827216348886</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>27.8983245115816</v>
       </c>
     </row>
     <row r="12">
@@ -1853,10 +1853,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
         <v>26.68684784454105</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
         <v>17.47216389248049</v>
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.171846905972197</v>
+        <v>4.055599766243573</v>
       </c>
       <c r="C2" t="n">
-        <v>4.498367980858886</v>
+        <v>4.738896168399354</v>
       </c>
       <c r="D2" t="n">
-        <v>12.91390930166254</v>
+        <v>22.05692567131309</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.09409321535422</v>
+        <v>22.67346322958009</v>
       </c>
       <c r="C3" t="n">
-        <v>39.95713156284518</v>
+        <v>48.15472489330605</v>
       </c>
       <c r="D3" t="n">
-        <v>76.15907815694632</v>
+        <v>110.1962710631832</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.95632974159018</v>
+        <v>31.43457974227862</v>
       </c>
       <c r="C4" t="n">
-        <v>102.9951516525329</v>
+        <v>121.7435875605342</v>
       </c>
       <c r="D4" t="n">
-        <v>113.9328028255466</v>
+        <v>152.6166076159836</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.20256848890689</v>
+        <v>34.50843180427539</v>
       </c>
       <c r="C5" t="n">
-        <v>134.9412219487241</v>
+        <v>139.5554361586841</v>
       </c>
       <c r="D5" t="n">
-        <v>75.66820430482292</v>
+        <v>94.91045930806041</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.74096714146165</v>
+        <v>33.52962934314132</v>
       </c>
       <c r="C6" t="n">
-        <v>133.8770074373206</v>
+        <v>157.2229678443097</v>
       </c>
       <c r="D6" t="n">
-        <v>36.95102009244145</v>
+        <v>40.89568236810514</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.17611805415445</v>
+        <v>18.92416874706152</v>
       </c>
       <c r="C7" t="n">
-        <v>126.0014273538526</v>
+        <v>150.195617777311</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.01520924164921</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>91.12582190818894</v>
+        <v>105.7293190088602</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>49.03437083631118</v>
+        <v>47.03749600587317</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>27.98864530037232</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2192,10 +2192,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.980807014271569</v>
+        <v>4.50327671938012</v>
       </c>
       <c r="C2" t="n">
-        <v>5.82961786781756</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="D2" t="n">
-        <v>19.33944802595792</v>
+        <v>25.58139992955914</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.27232932917064</v>
+        <v>18.27032477603314</v>
       </c>
       <c r="C3" t="n">
-        <v>28.15161541927729</v>
+        <v>32.86400439966197</v>
       </c>
       <c r="D3" t="n">
-        <v>69.97897635871264</v>
+        <v>103.8590896322701</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.78813208899449</v>
+        <v>36.45032876327557</v>
       </c>
       <c r="C4" t="n">
-        <v>101.2849471517349</v>
+        <v>121.9988419636384</v>
       </c>
       <c r="D4" t="n">
-        <v>124.181267110179</v>
+        <v>168.5317196495287</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.00746273766904</v>
+        <v>40.07985002587604</v>
       </c>
       <c r="C5" t="n">
-        <v>161.8165653524806</v>
+        <v>178.4081015542516</v>
       </c>
       <c r="D5" t="n">
-        <v>95.37678946757764</v>
+        <v>119.6995888402924</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.73846386670541</v>
+        <v>39.44662275663685</v>
       </c>
       <c r="C6" t="n">
-        <v>173.3236301939574</v>
+        <v>186.002901794305</v>
       </c>
       <c r="D6" t="n">
-        <v>48.98626519880311</v>
+        <v>56.87558975013048</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.13536767666159</v>
+        <v>26.58965482182061</v>
       </c>
       <c r="C7" t="n">
-        <v>157.5017841923158</v>
+        <v>186.0078105328262</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.27246819789088</v>
+        <v>13.10142311317368</v>
       </c>
       <c r="C8" t="n">
-        <v>126.6749062789659</v>
+        <v>146.285316671296</v>
       </c>
       <c r="D8" t="n">
-        <v>29.70768553050848</v>
+        <v>28.53940576245478</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>77.43436842476289</v>
+        <v>80.42968067041991</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>43.70249905454677</v>
+        <v>41.14013754646259</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>31.62994753542373</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>14.46605242207675</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.550981446260713</v>
+        <v>2.76067454434203</v>
       </c>
       <c r="C2" t="n">
-        <v>2.767546778271758</v>
+        <v>3.217187226816798</v>
       </c>
       <c r="D2" t="n">
-        <v>13.47743248390021</v>
+        <v>18.04648629946487</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.98900515327081</v>
+        <v>18.53539665617978</v>
       </c>
       <c r="C3" t="n">
-        <v>27.62638039750524</v>
+        <v>31.98043146583985</v>
       </c>
       <c r="D3" t="n">
-        <v>71.18652603493622</v>
+        <v>104.0063517879071</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.68901662859457</v>
+        <v>39.74311056331938</v>
       </c>
       <c r="C4" t="n">
-        <v>99.72789529279949</v>
+        <v>120.2886374628405</v>
       </c>
       <c r="D4" t="n">
-        <v>131.826136483149</v>
+        <v>180.4776257148039</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.53546307610458</v>
+        <v>41.77336481570179</v>
       </c>
       <c r="C5" t="n">
-        <v>192.3243752619502</v>
+        <v>217.8007281871549</v>
       </c>
       <c r="D5" t="n">
-        <v>100.7273144557228</v>
+        <v>122.8902688790945</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.57366912111219</v>
+        <v>31.79880814055419</v>
       </c>
       <c r="C6" t="n">
-        <v>209.8318820717836</v>
+        <v>218.9690079552086</v>
       </c>
       <c r="D6" t="n">
-        <v>48.26173539306896</v>
+        <v>55.02401357992099</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.77958979262998</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>166.424889076215</v>
+        <v>191.5173786490593</v>
       </c>
       <c r="D7" t="n">
-        <v>34.01559445674349</v>
+        <v>34.13536767666159</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>95.54859531582082</v>
+        <v>100.8058542720625</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>33.28124717396686</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.1930287493049</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.06125357275758</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>19.01350778814797</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.56743447752142</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>14.53673825678252</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
         <v>12.18348900970292</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.955461500410399</v>
+        <v>3.232895190084747</v>
       </c>
       <c r="C2" t="n">
-        <v>6.904631603967817</v>
+        <v>6.969426952448107</v>
       </c>
       <c r="D2" t="n">
-        <v>14.07237159267378</v>
+        <v>20.79537987135594</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.28995973011808</v>
+        <v>14.25497666566369</v>
       </c>
       <c r="C3" t="n">
-        <v>19.06063167795183</v>
+        <v>22.44766125760332</v>
       </c>
       <c r="D3" t="n">
-        <v>65.88508843200344</v>
+        <v>95.41605937574751</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.90674363475911</v>
+        <v>37.5351599764683</v>
       </c>
       <c r="C4" t="n">
-        <v>84.52749558794612</v>
+        <v>102.1783375625995</v>
       </c>
       <c r="D4" t="n">
-        <v>137.7735640754761</v>
+        <v>188.7989192559999</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.21826075664162</v>
+        <v>49.13647259755287</v>
       </c>
       <c r="C5" t="n">
-        <v>189.9190933865455</v>
+        <v>221.0650393037756</v>
       </c>
       <c r="D5" t="n">
-        <v>119.65050145508</v>
+        <v>152.6126806251667</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.84413276586557</v>
+        <v>41.0164373357275</v>
       </c>
       <c r="C6" t="n">
-        <v>254.55147174793</v>
+        <v>273.6307566322625</v>
       </c>
       <c r="D6" t="n">
-        <v>63.31585468998956</v>
+        <v>72.57373554103698</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.81679839440012</v>
+        <v>17.42700349808513</v>
       </c>
       <c r="C7" t="n">
-        <v>228.1679839440012</v>
+        <v>243.2594096536832</v>
       </c>
       <c r="D7" t="n">
-        <v>38.80652325346792</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.842781498600267</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>146.7860080004618</v>
+        <v>160.6384681073843</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>64.45468202691582</v>
+        <v>62.12499472473814</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>23.91537407545231</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.900082718345077</v>
+        <v>2.133337761328319</v>
       </c>
       <c r="C2" t="n">
-        <v>3.588287859022092</v>
+        <v>4.038910055271378</v>
       </c>
       <c r="D2" t="n">
-        <v>9.879327147835653</v>
+        <v>14.91078413210056</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.44427404613408</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="C3" t="n">
-        <v>23.03670988015141</v>
+        <v>24.852943133008</v>
       </c>
       <c r="D3" t="n">
-        <v>62.83676181031709</v>
+        <v>91.33689766460201</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.23558805795278</v>
+        <v>34.42105625859742</v>
       </c>
       <c r="C4" t="n">
-        <v>70.28429989473339</v>
+        <v>85.59956408098364</v>
       </c>
       <c r="D4" t="n">
-        <v>139.4071922553428</v>
+        <v>192.2703791382166</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.4278149860027</v>
+        <v>52.69530802544756</v>
       </c>
       <c r="C5" t="n">
-        <v>183.2677526902733</v>
+        <v>216.6962620198773</v>
       </c>
       <c r="D5" t="n">
-        <v>135.0393967191488</v>
+        <v>173.1066639513189</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.78000036992004</v>
+        <v>47.13468902859362</v>
       </c>
       <c r="C6" t="n">
-        <v>282.7678825156876</v>
+        <v>310.0585051983405</v>
       </c>
       <c r="D6" t="n">
-        <v>75.27059648460298</v>
+        <v>86.78257006460107</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.31963314542373</v>
+        <v>15.51063197939536</v>
       </c>
       <c r="C7" t="n">
-        <v>280.5687676581747</v>
+        <v>295.1212138782251</v>
       </c>
       <c r="D7" t="n">
-        <v>43.83699849002857</v>
+        <v>45.09461729916874</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>188.8440796503952</v>
+        <v>200.6103258857932</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>74.77186865084555</v>
+        <v>66.22968187619405</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>24.48478774391545</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.558254590817941</v>
+        <v>3.811144587886118</v>
       </c>
       <c r="C2" t="n">
-        <v>10.45659479793278</v>
+        <v>10.16305223436298</v>
       </c>
       <c r="D2" t="n">
-        <v>11.06920536538279</v>
+        <v>17.85406374943249</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.25850274585317</v>
+        <v>10.32307711015521</v>
       </c>
       <c r="C3" t="n">
-        <v>18.83973844449629</v>
+        <v>20.85722997672349</v>
       </c>
       <c r="D3" t="n">
-        <v>57.20152998794041</v>
+        <v>83.75289664929539</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.9818551819006</v>
+        <v>29.73713796163589</v>
       </c>
       <c r="C4" t="n">
-        <v>64.42621134349268</v>
+        <v>75.55530331883452</v>
       </c>
       <c r="D4" t="n">
-        <v>138.6159036057199</v>
+        <v>192.5001081010103</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.25600913775951</v>
+        <v>52.03262832508096</v>
       </c>
       <c r="C5" t="n">
-        <v>160.0494194848363</v>
+        <v>190.6063167795183</v>
       </c>
       <c r="D5" t="n">
-        <v>148.8084082712103</v>
+        <v>192.3734626471625</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>72.57373554103698</v>
+        <v>55.34602682691394</v>
       </c>
       <c r="C6" t="n">
-        <v>287.1955646618407</v>
+        <v>327.125207288967</v>
       </c>
       <c r="D6" t="n">
-        <v>91.81402704886597</v>
+        <v>107.5121728397725</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.14777054391831</v>
+        <v>27.84727363096077</v>
       </c>
       <c r="C7" t="n">
-        <v>332.6102317125939</v>
+        <v>351.9536067293688</v>
       </c>
       <c r="D7" t="n">
-        <v>52.04146405441917</v>
+        <v>54.49681506274045</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>261.8615651537517</v>
+        <v>268.620898097491</v>
       </c>
       <c r="D8" t="n">
-        <v>37.1346069131356</v>
+        <v>35.29873870619407</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>132.4593637523881</v>
+        <v>127.6890516574529</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>51.24723016168351</v>
+        <v>45.26838664282043</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>25.58827216348886</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.590873249236338</v>
+        <v>7.17461222263569</v>
       </c>
       <c r="C2" t="n">
-        <v>7.656650345420874</v>
+        <v>8.663923489978101</v>
       </c>
       <c r="D2" t="n">
-        <v>6.367615609744812</v>
+        <v>12.88052987971815</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.262347621212151</v>
+        <v>2.813688920371358</v>
       </c>
       <c r="C2" t="n">
-        <v>5.938591862988956</v>
+        <v>6.016149931624454</v>
       </c>
       <c r="D2" t="n">
-        <v>8.14752419754428</v>
+        <v>13.28304643845934</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.02979658849267</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="C3" t="n">
-        <v>28.2252464970958</v>
+        <v>29.54569715930776</v>
       </c>
       <c r="D3" t="n">
-        <v>62.03663743135596</v>
+        <v>91.08655200001907</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.86769471076749</v>
+        <v>40.18980576875168</v>
       </c>
       <c r="C4" t="n">
-        <v>92.58077200588271</v>
+        <v>108.5469349200486</v>
       </c>
       <c r="D4" t="n">
-        <v>142.3170924507304</v>
+        <v>194.9760758111208</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.77965621255477</v>
+        <v>31.17048960983623</v>
       </c>
       <c r="C5" t="n">
-        <v>241.7553721707771</v>
+        <v>281.1725424962866</v>
       </c>
       <c r="D5" t="n">
-        <v>134.5730665596316</v>
+        <v>169.4251100603933</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.66797365398211</v>
+        <v>17.26796036999715</v>
       </c>
       <c r="C6" t="n">
-        <v>275.3615778348496</v>
+        <v>286.3100282326101</v>
       </c>
       <c r="D6" t="n">
-        <v>74.78757661411353</v>
+        <v>83.20017269180445</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.126506585127596</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>184.1513256240954</v>
+        <v>188.8823678108608</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>97.63480918734528</v>
+        <v>94.04652132832319</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>24.20008090968387</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>39.04999668412111</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>19.41406085148067</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>20.07183181332604</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>18.64829764216817</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="D11" t="n">
         <v>16.17036643664921</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.22115527536279</v>
+        <v>7.530004891573035</v>
       </c>
       <c r="C2" t="n">
-        <v>6.277294820954105</v>
+        <v>10.30049691295754</v>
       </c>
       <c r="D2" t="n">
-        <v>8.435176274888596</v>
+        <v>23.393084296793</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.11538856521139</v>
+        <v>15.2367243699105</v>
       </c>
       <c r="C3" t="n">
-        <v>19.29134238844982</v>
+        <v>21.82916020392783</v>
       </c>
       <c r="D3" t="n">
-        <v>8.482300164692441</v>
+        <v>13.95554361586841</v>
       </c>
     </row>
     <row r="4">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39829124928852</v>
+        <v>13.39707277514232</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14399536392226</v>
+        <v>70.13761629339217</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576269558739826</v>
+        <v>1.576126208840273</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.789366211943441</v>
+        <v>5.300455855228529</v>
       </c>
       <c r="C2" t="n">
-        <v>3.800345363139403</v>
+        <v>9.281442795949344</v>
       </c>
       <c r="D2" t="n">
-        <v>25.16710239836698</v>
+        <v>29.46715734296801</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.49813130114741</v>
+        <v>21.72116795646068</v>
       </c>
       <c r="C3" t="n">
-        <v>22.53601855098553</v>
+        <v>33.30579086657304</v>
       </c>
       <c r="D3" t="n">
-        <v>13.51375714895735</v>
+        <v>30.23292055228053</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.63357142660446</v>
+        <v>17.65084197465341</v>
       </c>
       <c r="C4" t="n">
-        <v>29.94134148411922</v>
+        <v>33.82120841130262</v>
       </c>
       <c r="D4" t="n">
-        <v>19.51419911731385</v>
+        <v>22.38581115223577</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4885,7 +4885,7 @@
         <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44182767623324</v>
+        <v>15.43566851220637</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14914387793281</v>
+        <v>86.11478222599347</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250911089733314</v>
+        <v>3.249614423622395</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.202281084803848</v>
+        <v>4.590652265058085</v>
       </c>
       <c r="C2" t="n">
-        <v>9.145961612763285</v>
+        <v>5.607742886657781</v>
       </c>
       <c r="D2" t="n">
-        <v>26.95682846320892</v>
+        <v>33.63958508601696</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.55427084673872</v>
+        <v>19.79694245613693</v>
       </c>
       <c r="C3" t="n">
-        <v>17.83835578616454</v>
+        <v>34.96003574822892</v>
       </c>
       <c r="D3" t="n">
-        <v>30.50780990946963</v>
+        <v>46.79009558440298</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.91054745238907</v>
+        <v>31.06446085777758</v>
       </c>
       <c r="C4" t="n">
-        <v>45.53738551378405</v>
+        <v>62.4990406000562</v>
       </c>
       <c r="D4" t="n">
-        <v>21.91359050649305</v>
+        <v>32.49388551516093</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.87976911619216</v>
+        <v>15.14345833800705</v>
       </c>
       <c r="C5" t="n">
-        <v>33.84575210390879</v>
+        <v>37.40458753180348</v>
       </c>
       <c r="D5" t="n">
-        <v>29.47697482001049</v>
+        <v>30.97414006898687</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
         <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
         <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.78845088416398</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.04418831335365</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73394186399888</v>
+        <v>16.71966350149693</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0770453703932</v>
+        <v>101.1539641840564</v>
       </c>
       <c r="D21" t="n">
-        <v>4.18348546599972</v>
+        <v>4.179915875374232</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.052474596681586</v>
+        <v>4.515057691831081</v>
       </c>
       <c r="C2" t="n">
-        <v>5.895394964002096</v>
+        <v>7.229590094073512</v>
       </c>
       <c r="D2" t="n">
-        <v>24.00667661194726</v>
+        <v>30.7944802391097</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.69385894719102</v>
+        <v>17.72054606165493</v>
       </c>
       <c r="C3" t="n">
-        <v>28.01907947920397</v>
+        <v>27.43493959517712</v>
       </c>
       <c r="D3" t="n">
-        <v>44.20809912223388</v>
+        <v>62.39497534340603</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.8414652601933</v>
+        <v>34.5486834601495</v>
       </c>
       <c r="C4" t="n">
-        <v>45.03963942773092</v>
+        <v>76.18067660643975</v>
       </c>
       <c r="D4" t="n">
-        <v>31.71535958569321</v>
+        <v>46.59669128666636</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.20761609614836</v>
+        <v>30.36054775383262</v>
       </c>
       <c r="C5" t="n">
-        <v>60.99107612633311</v>
+        <v>78.7361658805942</v>
       </c>
       <c r="D5" t="n">
-        <v>30.48326621686347</v>
+        <v>35.46563581591603</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.76606630894878</v>
+        <v>13.08178815908875</v>
       </c>
       <c r="C6" t="n">
-        <v>33.56988099901544</v>
+        <v>36.02523200733671</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>37.63529824230149</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D7" t="n">
         <v>39.76470901281281</v>
@@ -5532,10 +5532,10 @@
         <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.50312215512664</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>48.9695754878309</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.28806265463436</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.51560713784138</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05682833529587</v>
+        <v>18.02943186791728</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7993086635969</v>
+        <v>116.762034954131</v>
       </c>
       <c r="D21" t="n">
-        <v>6.018942778431956</v>
+        <v>6.009810622639094</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.249225048158447</v>
+        <v>6.880087911361648</v>
       </c>
       <c r="C2" t="n">
-        <v>8.533351045313276</v>
+        <v>10.32896759638069</v>
       </c>
       <c r="D2" t="n">
-        <v>21.86646661668921</v>
+        <v>33.60424216866407</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.04452280405637</v>
+        <v>14.57895340806514</v>
       </c>
       <c r="C3" t="n">
-        <v>23.56194490192345</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D3" t="n">
-        <v>49.50462798664542</v>
+        <v>66.99937207632358</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.47813649416398</v>
+        <v>24.93835518327748</v>
       </c>
       <c r="C4" t="n">
-        <v>49.44277788127786</v>
+        <v>59.55085224420302</v>
       </c>
       <c r="D4" t="n">
-        <v>40.10046672766521</v>
+        <v>56.41122308602172</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.83254741539708</v>
+        <v>24.83821691744431</v>
       </c>
       <c r="C5" t="n">
-        <v>53.75068680751288</v>
+        <v>82.63861300497527</v>
       </c>
       <c r="D5" t="n">
-        <v>27.95526587842793</v>
+        <v>35.41654843070369</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.93965572615122</v>
+        <v>14.53084777055704</v>
       </c>
       <c r="C6" t="n">
-        <v>45.16235789076178</v>
+        <v>54.58124536530568</v>
       </c>
       <c r="D6" t="n">
-        <v>30.5510068084565</v>
+        <v>30.83276839957533</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.228207435741766</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>22.51736534460484</v>
+        <v>23.1162314441954</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.52187317249857</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
         <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.056148086433458</v>
+        <v>7.039328407525477</v>
       </c>
       <c r="C21" t="n">
-        <v>66.15138831031368</v>
+        <v>65.99370382055135</v>
       </c>
       <c r="D21" t="n">
-        <v>4.410092554020911</v>
+        <v>4.399580254703423</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.959208564778139</v>
+        <v>6.316564729123979</v>
       </c>
       <c r="C2" t="n">
-        <v>6.911503837897546</v>
+        <v>5.179700887606172</v>
       </c>
       <c r="D2" t="n">
-        <v>20.01881743729671</v>
+        <v>25.38406864100553</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.59001467471911</v>
+        <v>20.12091919853838</v>
       </c>
       <c r="C3" t="n">
-        <v>29.86967390170921</v>
+        <v>34.94040079414398</v>
       </c>
       <c r="D3" t="n">
-        <v>55.91053175685585</v>
+        <v>79.03559893038948</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.64703815702343</v>
+        <v>27.29945841199106</v>
       </c>
       <c r="C4" t="n">
-        <v>55.55612083562275</v>
+        <v>63.04783756673017</v>
       </c>
       <c r="D4" t="n">
-        <v>56.36017220540089</v>
+        <v>78.43967807391167</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.05468443846411</v>
+        <v>31.95588777323368</v>
       </c>
       <c r="C5" t="n">
-        <v>76.82175785731292</v>
+        <v>98.96016858807852</v>
       </c>
       <c r="D5" t="n">
-        <v>37.01188845010476</v>
+        <v>48.35107443415542</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.29691407950582</v>
+        <v>25.27803988894688</v>
       </c>
       <c r="C6" t="n">
-        <v>68.50831829775093</v>
+        <v>97.69076880648737</v>
       </c>
       <c r="D6" t="n">
-        <v>33.04660947265189</v>
+        <v>35.05919226635785</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.59426046070558</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="C7" t="n">
-        <v>47.84940135728529</v>
+        <v>54.97590794241288</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>25.53525778745954</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.07499804061703</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.278146084445734</v>
+        <v>7.252557060312999</v>
       </c>
       <c r="C21" t="n">
-        <v>75.5107656261245</v>
+        <v>75.24527950074736</v>
       </c>
       <c r="D21" t="n">
-        <v>5.4586095633343</v>
+        <v>5.439417795234749</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.495823648373645</v>
+        <v>4.870450360768427</v>
       </c>
       <c r="C2" t="n">
-        <v>6.066219064541041</v>
+        <v>5.680392216772045</v>
       </c>
       <c r="D2" t="n">
-        <v>26.87632515146068</v>
+        <v>32.12867536918112</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.49536598448391</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="C3" t="n">
-        <v>28.06325812589508</v>
+        <v>26.35992585902686</v>
       </c>
       <c r="D3" t="n">
-        <v>58.95394964002097</v>
+        <v>80.74874867430016</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.25812719742145</v>
+        <v>33.5021404074224</v>
       </c>
       <c r="C4" t="n">
-        <v>66.91494177375834</v>
+        <v>76.06581212504287</v>
       </c>
       <c r="D4" t="n">
-        <v>71.72648727227197</v>
+        <v>98.46438599743385</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.12326790904115</v>
+        <v>37.11006322052944</v>
       </c>
       <c r="C5" t="n">
-        <v>91.64614819143976</v>
+        <v>108.6549271675158</v>
       </c>
       <c r="D5" t="n">
-        <v>48.54742397500478</v>
+        <v>65.55620295108078</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.7686360036298</v>
+        <v>34.61642405174254</v>
       </c>
       <c r="C6" t="n">
-        <v>97.36875555949442</v>
+        <v>129.4493252911675</v>
       </c>
       <c r="D6" t="n">
-        <v>37.59504658642736</v>
+        <v>42.18373535607696</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.25407703341745</v>
+        <v>21.55917958525995</v>
       </c>
       <c r="C7" t="n">
-        <v>76.41531430775473</v>
+        <v>99.53154575195012</v>
       </c>
       <c r="D7" t="n">
-        <v>35.09355343600648</v>
+        <v>35.87207936547421</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>46.48084505756524</v>
+        <v>50.65327280061418</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.28906009787183</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -6594,7 +6594,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.487475039357146</v>
+        <v>7.451794827036013</v>
       </c>
       <c r="C21" t="n">
-        <v>84.23409419276788</v>
+        <v>83.83269180415515</v>
       </c>
       <c r="D21" t="n">
-        <v>6.551540659437502</v>
+        <v>6.52032047365651</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_78_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_78_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497639959285</v>
+        <v>10.84497630359506</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907217668586</v>
+        <v>37.78907184218376</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.687264450701772</v>
+        <v>8.550040756285473</v>
       </c>
       <c r="C2" t="n">
-        <v>9.86165568915921</v>
+        <v>4.62304993929823</v>
       </c>
       <c r="D2" t="n">
-        <v>40.79554410227195</v>
+        <v>25.78069471352124</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.55503161026472</v>
+        <v>27.20913762320035</v>
       </c>
       <c r="C3" t="n">
-        <v>23.95955272214341</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D3" t="n">
-        <v>86.6932310235146</v>
+        <v>70.67110849020665</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.51414236405162</v>
+        <v>49.83842220608933</v>
       </c>
       <c r="C4" t="n">
-        <v>70.71823238001049</v>
+        <v>37.72660077879643</v>
       </c>
       <c r="D4" t="n">
-        <v>114.7240914751695</v>
+        <v>86.17388648796803</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.61414176116455</v>
+        <v>60.89290135590843</v>
       </c>
       <c r="C5" t="n">
-        <v>123.4056864238241</v>
+        <v>61.80101798233672</v>
       </c>
       <c r="D5" t="n">
-        <v>83.74307917225293</v>
+        <v>61.50649367106269</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.98247707670636</v>
+        <v>55.14476854754334</v>
       </c>
       <c r="C6" t="n">
-        <v>151.0242128396953</v>
+        <v>79.29576207201488</v>
       </c>
       <c r="D6" t="n">
-        <v>51.20010627187966</v>
+        <v>43.83405324691584</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.9014907388726</v>
+        <v>39.04606969330414</v>
       </c>
       <c r="C7" t="n">
-        <v>142.3504718726747</v>
+        <v>77.01418040734529</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.27246819789088</v>
+        <v>21.36283004441059</v>
       </c>
       <c r="C8" t="n">
-        <v>88.95615948180348</v>
+        <v>54.9091490985241</v>
       </c>
       <c r="D8" t="n">
-        <v>35.21529015133309</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>45.04062117543515</v>
+        <v>36.16562192904399</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.635262040016475</v>
+        <v>7.709945740792508</v>
       </c>
       <c r="C21" t="n">
-        <v>92.57755223519976</v>
+        <v>95.41057854230729</v>
       </c>
       <c r="D21" t="n">
-        <v>7.635262040016475</v>
+        <v>8.673688958391573</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.69708192774424</v>
+        <v>10.26809923871739</v>
       </c>
       <c r="C2" t="n">
-        <v>14.27559336745287</v>
+        <v>6.219371706403543</v>
       </c>
       <c r="D2" t="n">
-        <v>42.76002125846983</v>
+        <v>26.38643304704152</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.51085296357361</v>
+        <v>27.91599597025805</v>
       </c>
       <c r="C3" t="n">
-        <v>30.72870314292516</v>
+        <v>22.16295442337174</v>
       </c>
       <c r="D3" t="n">
-        <v>96.01492547533806</v>
+        <v>74.19067400993146</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.31444666946201</v>
+        <v>50.5403718146258</v>
       </c>
       <c r="C4" t="n">
-        <v>65.43446623575416</v>
+        <v>53.45027201001334</v>
       </c>
       <c r="D4" t="n">
-        <v>128.2270493993801</v>
+        <v>100.4043194610256</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.10563750809372</v>
+        <v>67.47061097436206</v>
       </c>
       <c r="C5" t="n">
-        <v>125.0746575210437</v>
+        <v>65.06532909895736</v>
       </c>
       <c r="D5" t="n">
-        <v>100.0891784479623</v>
+        <v>76.03635969391547</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.63029169278902</v>
+        <v>68.91083485649213</v>
       </c>
       <c r="C6" t="n">
-        <v>169.8217361329091</v>
+        <v>88.83540451418115</v>
       </c>
       <c r="D6" t="n">
-        <v>62.91333813124836</v>
+        <v>52.5284109157256</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.98618308334508</v>
+        <v>51.92169083450106</v>
       </c>
       <c r="C7" t="n">
-        <v>176.9649324290088</v>
+        <v>95.04005000502096</v>
       </c>
       <c r="D7" t="n">
-        <v>43.89688509998763</v>
+        <v>41.9206269713388</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.53249247079604</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="C8" t="n">
-        <v>131.9321652352076</v>
+        <v>78.44164156932014</v>
       </c>
       <c r="D8" t="n">
-        <v>37.55184968744049</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.42656152972862</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>73.66249374504666</v>
+        <v>51.58593311964863</v>
       </c>
       <c r="D9" t="n">
-        <v>34.61249706092553</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>40.00131020953629</v>
+        <v>37.15424186722054</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.50740899884213</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.0569667290421</v>
+        <v>29.13827186204534</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.801941186326613</v>
+        <v>7.899291135949759</v>
       </c>
       <c r="C21" t="n">
-        <v>100.4499927739551</v>
+        <v>104.6656075513343</v>
       </c>
       <c r="D21" t="n">
-        <v>8.777183834617439</v>
+        <v>9.874113919937198</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.884014902178635</v>
+        <v>12.18152551429442</v>
       </c>
       <c r="C2" t="n">
-        <v>13.26930197059989</v>
+        <v>5.16497467204247</v>
       </c>
       <c r="D2" t="n">
-        <v>38.24005482811751</v>
+        <v>32.53119192792231</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.22614612934204</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="C3" t="n">
-        <v>41.09105016125025</v>
+        <v>23.00234871050277</v>
       </c>
       <c r="D3" t="n">
-        <v>103.2111361474672</v>
+        <v>76.71376560984577</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.20409001595887</v>
+        <v>50.99982974021331</v>
       </c>
       <c r="C4" t="n">
-        <v>69.26328228231672</v>
+        <v>54.25432337979149</v>
       </c>
       <c r="D4" t="n">
-        <v>139.4071922553428</v>
+        <v>110.588970144882</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.43099690882691</v>
+        <v>71.56940763959248</v>
       </c>
       <c r="C5" t="n">
-        <v>121.5649094783613</v>
+        <v>79.74245727744719</v>
       </c>
       <c r="D5" t="n">
-        <v>115.7725980233051</v>
+        <v>91.6952355766521</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.2252718592916</v>
+        <v>78.57123226628075</v>
       </c>
       <c r="C6" t="n">
-        <v>180.2469150043059</v>
+        <v>94.83290123942491</v>
       </c>
       <c r="D6" t="n">
-        <v>75.67311304334416</v>
+        <v>61.70578845502478</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.65166915810418</v>
+        <v>65.27640485537042</v>
       </c>
       <c r="C7" t="n">
-        <v>205.7703918193145</v>
+        <v>110.9698882541297</v>
       </c>
       <c r="D7" t="n">
-        <v>49.34656660626167</v>
+        <v>46.77144237802229</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.70906818884022</v>
+        <v>42.72566008882119</v>
       </c>
       <c r="C8" t="n">
-        <v>172.1543686781994</v>
+        <v>99.80447161373074</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.19687362466387</v>
+        <v>22.63124807829746</v>
       </c>
       <c r="C9" t="n">
-        <v>108.7187407682918</v>
+        <v>72.66405632982764</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>37.60780930658255</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>10.2494460323367</v>
       </c>
       <c r="C10" t="n">
-        <v>58.64960785170445</v>
+        <v>47.83074815090461</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>36.96083756948391</v>
+        <v>37.6716229073586</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.13827186204534</v>
+        <v>32.00006641992479</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>34.08137155292803</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.952074715929364</v>
+        <v>8.07399774625223</v>
       </c>
       <c r="C21" t="n">
-        <v>107.3530086650464</v>
+        <v>113.0359684475312</v>
       </c>
       <c r="D21" t="n">
-        <v>9.940093394911704</v>
+        <v>11.10174690109681</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.384305320717008</v>
+        <v>10.96415836102838</v>
       </c>
       <c r="C2" t="n">
-        <v>9.3413294059084</v>
+        <v>3.429244730934109</v>
       </c>
       <c r="D2" t="n">
-        <v>31.7801549341735</v>
+        <v>26.35305362509713</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.38875639534851</v>
+        <v>36.84990007890403</v>
       </c>
       <c r="C3" t="n">
-        <v>57.57950285407543</v>
+        <v>33.60522391636832</v>
       </c>
       <c r="D3" t="n">
-        <v>110.1226399853647</v>
+        <v>84.65610453720245</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.73865948868787</v>
+        <v>34.3827680981318</v>
       </c>
       <c r="C4" t="n">
-        <v>96.58826613461819</v>
+        <v>71.05006310404592</v>
       </c>
       <c r="D4" t="n">
-        <v>131.8516619234594</v>
+        <v>105.7518992060579</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.09685853201772</v>
+        <v>44.25227776892498</v>
       </c>
       <c r="C5" t="n">
-        <v>107.6977231558751</v>
+        <v>56.64684253504097</v>
       </c>
       <c r="D5" t="n">
-        <v>75.22641783791185</v>
+        <v>62.39006660488482</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.94094057349173</v>
+        <v>40.53341746523807</v>
       </c>
       <c r="C6" t="n">
-        <v>135.5273253281594</v>
+        <v>73.05675541152641</v>
       </c>
       <c r="D6" t="n">
-        <v>32.48308629041422</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.36144738607885</v>
+        <v>28.32636651063322</v>
       </c>
       <c r="C7" t="n">
-        <v>121.030838727251</v>
+        <v>70.18710687201296</v>
       </c>
       <c r="D7" t="n">
-        <v>28.20659329071511</v>
+        <v>28.62579956042849</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>15.68832831386403</v>
       </c>
       <c r="C8" t="n">
-        <v>80.11061266653972</v>
+        <v>53.49052366588747</v>
       </c>
       <c r="D8" t="n">
-        <v>26.20284622634736</v>
+        <v>27.70492021384499</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>44.70780870369548</v>
+        <v>36.49843440078366</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>25.58827216348886</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>27.8983245115816</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6145740628585034</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.27567548291088</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.055599766243573</v>
+        <v>6.658212930201868</v>
       </c>
       <c r="C2" t="n">
-        <v>4.738896168399354</v>
+        <v>2.017491532227195</v>
       </c>
       <c r="D2" t="n">
-        <v>22.05692567131309</v>
+        <v>18.32039390894973</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.67346322958009</v>
+        <v>38.50905369908114</v>
       </c>
       <c r="C3" t="n">
-        <v>48.15472489330605</v>
+        <v>23.53740120931728</v>
       </c>
       <c r="D3" t="n">
-        <v>110.1962710631832</v>
+        <v>87.23810099937157</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.43457974227862</v>
+        <v>50.77010077741955</v>
       </c>
       <c r="C4" t="n">
-        <v>121.7435875605342</v>
+        <v>79.44793296617313</v>
       </c>
       <c r="D4" t="n">
-        <v>152.6166076159836</v>
+        <v>121.1054515527738</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.50843180427539</v>
+        <v>49.94641445355649</v>
       </c>
       <c r="C5" t="n">
-        <v>139.5554361586841</v>
+        <v>92.72607066611126</v>
       </c>
       <c r="D5" t="n">
-        <v>94.91045930806041</v>
+        <v>81.2150788338174</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.52962934314132</v>
+        <v>49.26802678992194</v>
       </c>
       <c r="C6" t="n">
-        <v>157.2229678443097</v>
+        <v>84.68948395914687</v>
       </c>
       <c r="D6" t="n">
-        <v>40.89568236810514</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.92416874706152</v>
+        <v>26.82920126165683</v>
       </c>
       <c r="C7" t="n">
-        <v>150.195617777311</v>
+        <v>86.59603800079415</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>12.93452600345173</v>
       </c>
       <c r="C8" t="n">
-        <v>105.7293190088602</v>
+        <v>69.59609475405638</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>47.03749600587317</v>
+        <v>42.93280885441725</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.50327671938012</v>
+        <v>7.452446822937538</v>
       </c>
       <c r="C2" t="n">
-        <v>6.548257187326225</v>
+        <v>5.072690387843269</v>
       </c>
       <c r="D2" t="n">
-        <v>25.58139992955914</v>
+        <v>18.07888397370501</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.27032477603314</v>
+        <v>30.35563901531138</v>
       </c>
       <c r="C3" t="n">
-        <v>32.86400439966197</v>
+        <v>14.75075925630833</v>
       </c>
       <c r="D3" t="n">
-        <v>103.8590896322701</v>
+        <v>81.86303231862028</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.45032876327557</v>
+        <v>63.04783756673017</v>
       </c>
       <c r="C4" t="n">
-        <v>121.9988419636384</v>
+        <v>69.0846042001438</v>
       </c>
       <c r="D4" t="n">
-        <v>168.5317196495287</v>
+        <v>135.6804779700219</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.07985002587604</v>
+        <v>62.70913460876503</v>
       </c>
       <c r="C5" t="n">
-        <v>178.4081015542516</v>
+        <v>120.1904626924158</v>
       </c>
       <c r="D5" t="n">
-        <v>119.6995888402924</v>
+        <v>103.4762080276138</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.44662275663685</v>
+        <v>58.76741757621409</v>
       </c>
       <c r="C6" t="n">
-        <v>186.002901794305</v>
+        <v>116.3272854762046</v>
       </c>
       <c r="D6" t="n">
-        <v>56.87558975013048</v>
+        <v>52.20639766873265</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.58965482182061</v>
+        <v>40.12402867256714</v>
       </c>
       <c r="C7" t="n">
-        <v>186.0078105328262</v>
+        <v>105.1608870881013</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>34.43480072645687</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.10142311317368</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="C8" t="n">
-        <v>146.285316671296</v>
+        <v>91.70996179221579</v>
       </c>
       <c r="D8" t="n">
-        <v>28.53940576245478</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>80.42968067041991</v>
+        <v>62.67968217763759</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>3.131775176547325</v>
       </c>
       <c r="C10" t="n">
-        <v>41.14013754646259</v>
+        <v>41.28249096357838</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>31.62994753542373</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.95125677215293</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>36.10868056219768</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.76067454434203</v>
+        <v>4.367795536194059</v>
       </c>
       <c r="C2" t="n">
-        <v>3.217187226816798</v>
+        <v>2.242311756499715</v>
       </c>
       <c r="D2" t="n">
-        <v>18.04648629946487</v>
+        <v>12.46328710541326</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.53539665617978</v>
+        <v>30.9643225919444</v>
       </c>
       <c r="C3" t="n">
-        <v>31.98043146583985</v>
+        <v>18.04943154257761</v>
       </c>
       <c r="D3" t="n">
-        <v>104.0063517879071</v>
+        <v>80.85183218324607</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.74311056331938</v>
+        <v>69.88865556992194</v>
       </c>
       <c r="C4" t="n">
-        <v>120.2886374628405</v>
+        <v>63.35414285045516</v>
       </c>
       <c r="D4" t="n">
-        <v>180.4776257148039</v>
+        <v>145.4694843290669</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.77336481570179</v>
+        <v>65.38439710283758</v>
       </c>
       <c r="C5" t="n">
-        <v>217.8007281871549</v>
+        <v>140.119941088626</v>
       </c>
       <c r="D5" t="n">
-        <v>122.8902688790945</v>
+        <v>112.4591995214722</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.79880814055419</v>
+        <v>49.87180162803373</v>
       </c>
       <c r="C6" t="n">
-        <v>218.9690079552086</v>
+        <v>146.4757757259199</v>
       </c>
       <c r="D6" t="n">
-        <v>55.02401357992099</v>
+        <v>51.4818678629985</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>12.93550775115597</v>
       </c>
       <c r="C7" t="n">
-        <v>191.5173786490593</v>
+        <v>114.6828580715911</v>
       </c>
       <c r="D7" t="n">
-        <v>34.13536767666159</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>100.8058542720625</v>
+        <v>76.68922191723958</v>
       </c>
       <c r="D8" t="n">
-        <v>30.62561963397925</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>23.91537407545231</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.01350778814797</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
-        <v>22.56743447752142</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.53673825678252</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.232895190084747</v>
+        <v>5.413356841216912</v>
       </c>
       <c r="C2" t="n">
-        <v>6.969426952448107</v>
+        <v>3.365431130158066</v>
       </c>
       <c r="D2" t="n">
-        <v>20.79537987135594</v>
+        <v>13.46957850226624</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.25497666566369</v>
+        <v>22.81090790817464</v>
       </c>
       <c r="C3" t="n">
-        <v>22.44766125760332</v>
+        <v>13.06706194352505</v>
       </c>
       <c r="D3" t="n">
-        <v>95.41605937574751</v>
+        <v>73.39545836949155</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.5351599764683</v>
+        <v>65.71524607916875</v>
       </c>
       <c r="C4" t="n">
-        <v>102.1783375625995</v>
+        <v>54.4330014619644</v>
       </c>
       <c r="D4" t="n">
-        <v>188.7989192559999</v>
+        <v>151.6083527237222</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.13647259755287</v>
+        <v>83.37492378316038</v>
       </c>
       <c r="C5" t="n">
-        <v>221.0650393037756</v>
+        <v>129.9343086570654</v>
       </c>
       <c r="D5" t="n">
-        <v>152.6126806251667</v>
+        <v>134.7203287152686</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.0164373357275</v>
+        <v>66.37498053642261</v>
       </c>
       <c r="C6" t="n">
-        <v>273.6307566322625</v>
+        <v>183.2657891948649</v>
       </c>
       <c r="D6" t="n">
-        <v>72.57373554103698</v>
+        <v>69.9171262533451</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>29.04500583014188</v>
       </c>
       <c r="C7" t="n">
-        <v>243.2594096536832</v>
+        <v>160.3763414703505</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>40.54323494228053</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>160.6384681073843</v>
+        <v>109.9017467519092</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>62.12499472473814</v>
+        <v>56.57812019574367</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.21204180858408</v>
+        <v>25.23287949455151</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>22.1305567491316</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.133337761328319</v>
+        <v>4.171445995344697</v>
       </c>
       <c r="C2" t="n">
-        <v>4.038910055271378</v>
+        <v>2.269800692218626</v>
       </c>
       <c r="D2" t="n">
-        <v>14.91078413210056</v>
+        <v>10.2199936012093</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.00815708127024</v>
+        <v>21.24502031990098</v>
       </c>
       <c r="C3" t="n">
-        <v>24.852943133008</v>
+        <v>13.35667751627786</v>
       </c>
       <c r="D3" t="n">
-        <v>91.33689766460201</v>
+        <v>68.50635480234243</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.42105625859742</v>
+        <v>58.65746183333842</v>
       </c>
       <c r="C4" t="n">
-        <v>85.59956408098364</v>
+        <v>45.49909735331843</v>
       </c>
       <c r="D4" t="n">
-        <v>192.2703791382166</v>
+        <v>154.0970831539879</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.69530802544756</v>
+        <v>92.38245896962486</v>
       </c>
       <c r="C5" t="n">
-        <v>216.6962620198773</v>
+        <v>122.2766765639403</v>
       </c>
       <c r="D5" t="n">
-        <v>173.1066639513189</v>
+        <v>152.7599427808037</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.13468902859362</v>
+        <v>79.49702035138549</v>
       </c>
       <c r="C6" t="n">
-        <v>310.0585051983405</v>
+        <v>200.8960144677291</v>
       </c>
       <c r="D6" t="n">
-        <v>86.78257006460107</v>
+        <v>85.61527204425161</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.51063197939536</v>
+        <v>29.22466566001905</v>
       </c>
       <c r="C7" t="n">
-        <v>295.1212138782251</v>
+        <v>202.1173086118121</v>
       </c>
       <c r="D7" t="n">
-        <v>45.09461729916874</v>
+        <v>45.51382356888213</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="C8" t="n">
-        <v>200.6103258857932</v>
+        <v>142.5301317025519</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>66.22968187619405</v>
+        <v>69.0031191406913</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.67895280517806</v>
+        <v>25.05518316008284</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.811144587886118</v>
+        <v>7.202101158354601</v>
       </c>
       <c r="C2" t="n">
-        <v>10.16305223436298</v>
+        <v>3.706097583531709</v>
       </c>
       <c r="D2" t="n">
-        <v>17.85406374943249</v>
+        <v>12.22864940409827</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.32307711015521</v>
+        <v>17.72545480017616</v>
       </c>
       <c r="C3" t="n">
-        <v>20.85722997672349</v>
+        <v>11.15265392024377</v>
       </c>
       <c r="D3" t="n">
-        <v>83.75289664929539</v>
+        <v>61.78138302825178</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.73713796163589</v>
+        <v>49.86394764639974</v>
       </c>
       <c r="C4" t="n">
-        <v>75.55530331883452</v>
+        <v>39.69205968269854</v>
       </c>
       <c r="D4" t="n">
-        <v>192.5001081010103</v>
+        <v>153.1015909818816</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.03262832508096</v>
+        <v>90.93438110586082</v>
       </c>
       <c r="C5" t="n">
-        <v>190.6063167795183</v>
+        <v>104.7033926579224</v>
       </c>
       <c r="D5" t="n">
-        <v>192.3734626471625</v>
+        <v>168.7869740526329</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.34602682691394</v>
+        <v>98.25429198872504</v>
       </c>
       <c r="C6" t="n">
-        <v>327.125207288967</v>
+        <v>198.9236833298972</v>
       </c>
       <c r="D6" t="n">
-        <v>107.5121728397725</v>
+        <v>106.6266364105418</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.84727363096077</v>
+        <v>53.53862930339555</v>
       </c>
       <c r="C7" t="n">
-        <v>351.9536067293688</v>
+        <v>240.8639452553209</v>
       </c>
       <c r="D7" t="n">
-        <v>54.49681506274045</v>
+        <v>55.45500082208532</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>14.85384276525424</v>
       </c>
       <c r="C8" t="n">
-        <v>268.620898097491</v>
+        <v>197.0220380267711</v>
       </c>
       <c r="D8" t="n">
-        <v>35.29873870619407</v>
+        <v>38.63668090063322</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>127.6890516574529</v>
+        <v>112.0468654856884</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>45.26838664282043</v>
+        <v>51.67429041303087</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>27.18950266911542</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.58827216348886</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>25.05518316008284</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.17076734727672</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.17461222263569</v>
+        <v>9.210756961243575</v>
       </c>
       <c r="C2" t="n">
-        <v>8.663923489978101</v>
+        <v>5.316163818496478</v>
       </c>
       <c r="D2" t="n">
-        <v>12.88052987971815</v>
+        <v>6.567892141411161</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.813688920371358</v>
+        <v>4.988260085278044</v>
       </c>
       <c r="C2" t="n">
-        <v>6.016149931624454</v>
+        <v>2.015528036818702</v>
       </c>
       <c r="D2" t="n">
-        <v>13.28304643845934</v>
+        <v>8.90150643440583</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.9113649691773</v>
+        <v>24.852943133008</v>
       </c>
       <c r="C3" t="n">
-        <v>29.54569715930776</v>
+        <v>13.95063487734718</v>
       </c>
       <c r="D3" t="n">
-        <v>91.08655200001907</v>
+        <v>67.1024555852695</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.18980576875168</v>
+        <v>69.11012964045422</v>
       </c>
       <c r="C4" t="n">
-        <v>108.5469349200486</v>
+        <v>57.15146085502382</v>
       </c>
       <c r="D4" t="n">
-        <v>194.9760758111208</v>
+        <v>158.3725944059827</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.17048960983623</v>
+        <v>59.54299826256906</v>
       </c>
       <c r="C5" t="n">
-        <v>281.1725424962866</v>
+        <v>162.8719441345459</v>
       </c>
       <c r="D5" t="n">
-        <v>169.4251100603933</v>
+        <v>154.3552828002048</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.26796036999715</v>
+        <v>33.24786775202249</v>
       </c>
       <c r="C6" t="n">
-        <v>286.3100282326101</v>
+        <v>203.4721204436727</v>
       </c>
       <c r="D6" t="n">
-        <v>83.20017269180445</v>
+        <v>84.68948395914687</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>188.8823678108608</v>
+        <v>138.5177288352952</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>94.04652132832319</v>
+        <v>82.5306207575081</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>25.36836067773758</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>39.38280915586078</v>
       </c>
       <c r="D9" t="n">
-        <v>19.41406085148067</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.07183181332604</v>
+        <v>23.77302065833652</v>
       </c>
       <c r="D10" t="n">
-        <v>18.64829764216817</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.57109942643116</v>
+        <v>17.41424077792992</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.8811517745239</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.53116656572653</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.530004891573035</v>
+        <v>7.820602212030092</v>
       </c>
       <c r="C2" t="n">
-        <v>10.30049691295754</v>
+        <v>2.928553401768235</v>
       </c>
       <c r="D2" t="n">
-        <v>23.393084296793</v>
+        <v>12.84322346695677</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.2367243699105</v>
+        <v>19.55150553007523</v>
       </c>
       <c r="C3" t="n">
-        <v>21.82916020392783</v>
+        <v>13.39594742444773</v>
       </c>
       <c r="D3" t="n">
-        <v>13.95554361586841</v>
+        <v>8.654106012935634</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39707277514232</v>
+        <v>13.39838064225535</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13761629339217</v>
+        <v>70.14446336239568</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576126208840273</v>
+        <v>1.576280075559453</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.300455855228529</v>
+        <v>5.184609626127406</v>
       </c>
       <c r="C2" t="n">
-        <v>9.281442795949344</v>
+        <v>5.227806525114265</v>
       </c>
       <c r="D2" t="n">
-        <v>29.46715734296801</v>
+        <v>16.0800456478585</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.72116795646068</v>
+        <v>24.11172361630166</v>
       </c>
       <c r="C3" t="n">
-        <v>33.30579086657304</v>
+        <v>12.15894531709675</v>
       </c>
       <c r="D3" t="n">
-        <v>30.23292055228053</v>
+        <v>17.34748193404114</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.65084197465341</v>
+        <v>22.51343835378785</v>
       </c>
       <c r="C4" t="n">
-        <v>33.82120841130262</v>
+        <v>20.9436237746972</v>
       </c>
       <c r="D4" t="n">
-        <v>22.38581115223577</v>
+        <v>19.60353815840031</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>39.82655911818034</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43566851220637</v>
+        <v>15.44223371823817</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11478222599347</v>
+        <v>86.15140916490769</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249614423622395</v>
+        <v>3.250996572260668</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.590652265058085</v>
+        <v>5.571418221600648</v>
       </c>
       <c r="C2" t="n">
-        <v>5.607742886657781</v>
+        <v>3.425317740117121</v>
       </c>
       <c r="D2" t="n">
-        <v>33.63958508601696</v>
+        <v>24.35814229006761</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.79694245613693</v>
+        <v>20.63633674326795</v>
       </c>
       <c r="C3" t="n">
-        <v>34.96003574822892</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D3" t="n">
-        <v>46.79009558440298</v>
+        <v>26.18321127226244</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.06446085777758</v>
+        <v>36.14402347955058</v>
       </c>
       <c r="C4" t="n">
-        <v>62.4990406000562</v>
+        <v>26.54645792283375</v>
       </c>
       <c r="D4" t="n">
-        <v>32.49388551516093</v>
+        <v>23.89181213055038</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.14345833800705</v>
+        <v>19.21771131063132</v>
       </c>
       <c r="C5" t="n">
-        <v>37.40458753180348</v>
+        <v>24.29825568010856</v>
       </c>
       <c r="D5" t="n">
-        <v>30.97414006898687</v>
+        <v>29.50151851261666</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>40.93593402397924</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.71966350149693</v>
+        <v>16.73816706119253</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1539641840564</v>
+        <v>102.1028190732744</v>
       </c>
       <c r="D21" t="n">
-        <v>4.179915875374232</v>
+        <v>5.021450118357758</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.515057691831081</v>
+        <v>8.569675710370408</v>
       </c>
       <c r="C2" t="n">
-        <v>7.229590094073512</v>
+        <v>3.767947688899258</v>
       </c>
       <c r="D2" t="n">
-        <v>30.7944802391097</v>
+        <v>24.04201952930014</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.72054606165493</v>
+        <v>19.7920337176157</v>
       </c>
       <c r="C3" t="n">
-        <v>27.43493959517712</v>
+        <v>14.90293015046658</v>
       </c>
       <c r="D3" t="n">
-        <v>62.39497534340603</v>
+        <v>38.86739161113123</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.5486834601495</v>
+        <v>38.10948238345269</v>
       </c>
       <c r="C4" t="n">
-        <v>76.18067660643975</v>
+        <v>35.39102299039327</v>
       </c>
       <c r="D4" t="n">
-        <v>46.59669128666636</v>
+        <v>30.98788453684632</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.36054775383262</v>
+        <v>37.18369429834795</v>
       </c>
       <c r="C5" t="n">
-        <v>78.7361658805942</v>
+        <v>37.89546138392689</v>
       </c>
       <c r="D5" t="n">
-        <v>35.46563581591603</v>
+        <v>31.58773238414113</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.08178815908875</v>
+        <v>15.8994040702771</v>
       </c>
       <c r="C6" t="n">
-        <v>36.02523200733671</v>
+        <v>26.12332466230338</v>
       </c>
       <c r="D6" t="n">
-        <v>37.63529824230149</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.50312215512664</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9695754878309</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>50.28806265463436</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
         <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.02943186791728</v>
+        <v>18.06799916611409</v>
       </c>
       <c r="C21" t="n">
-        <v>116.762034954131</v>
+        <v>117.8721850360776</v>
       </c>
       <c r="D21" t="n">
-        <v>6.009810622639094</v>
+        <v>6.883047301376794</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.880087911361648</v>
+        <v>9.016370915802707</v>
       </c>
       <c r="C2" t="n">
-        <v>10.32896759638069</v>
+        <v>4.178318229274425</v>
       </c>
       <c r="D2" t="n">
-        <v>33.60424216866407</v>
+        <v>30.20248637344887</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.57895340806514</v>
+        <v>22.62437584436775</v>
       </c>
       <c r="C3" t="n">
-        <v>26.01631416254048</v>
+        <v>13.87700379952867</v>
       </c>
       <c r="D3" t="n">
-        <v>66.99937207632358</v>
+        <v>45.62181581634928</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.93835518327748</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="C4" t="n">
-        <v>59.55085224420302</v>
+        <v>30.56671477172444</v>
       </c>
       <c r="D4" t="n">
-        <v>56.41122308602172</v>
+        <v>37.11399021134642</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.83821691744431</v>
+        <v>29.01064466049325</v>
       </c>
       <c r="C5" t="n">
-        <v>82.63861300497527</v>
+        <v>39.34353924769093</v>
       </c>
       <c r="D5" t="n">
-        <v>35.41654843070369</v>
+        <v>28.96155727528091</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.53084777055704</v>
+        <v>18.31450342272425</v>
       </c>
       <c r="C6" t="n">
-        <v>54.58124536530568</v>
+        <v>29.66547037922588</v>
       </c>
       <c r="D6" t="n">
-        <v>30.83276839957533</v>
+        <v>30.47050349670826</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.048547605864599</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>23.1162314441954</v>
+        <v>19.10382857693868</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.52187317249857</v>
+        <v>22.2984356065578</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.47308888692249</v>
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>27.95035713990669</v>
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.039328407525477</v>
+        <v>7.064139247869128</v>
       </c>
       <c r="C21" t="n">
-        <v>65.99370382055135</v>
+        <v>66.22630544877308</v>
       </c>
       <c r="D21" t="n">
-        <v>4.399580254703423</v>
+        <v>5.298104435901846</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.316564729123979</v>
+        <v>7.077419199915256</v>
       </c>
       <c r="C2" t="n">
-        <v>5.179700887606172</v>
+        <v>3.991786165467531</v>
       </c>
       <c r="D2" t="n">
-        <v>25.38406864100553</v>
+        <v>21.19691468239288</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.12091919853838</v>
+        <v>28.33814748308418</v>
       </c>
       <c r="C3" t="n">
-        <v>34.94040079414398</v>
+        <v>15.49197877301467</v>
       </c>
       <c r="D3" t="n">
-        <v>79.03559893038948</v>
+        <v>60.73582172322892</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.29945841199106</v>
+        <v>38.50512670826415</v>
       </c>
       <c r="C4" t="n">
-        <v>63.04783756673017</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D4" t="n">
-        <v>78.43967807391167</v>
+        <v>53.19501760690918</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.95588777323368</v>
+        <v>37.23278168356029</v>
       </c>
       <c r="C5" t="n">
-        <v>98.96016858807852</v>
+        <v>49.70097752749479</v>
       </c>
       <c r="D5" t="n">
-        <v>48.35107443415542</v>
+        <v>36.61918936840603</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.27803988894688</v>
+        <v>30.59125846433062</v>
       </c>
       <c r="C6" t="n">
-        <v>97.69076880648737</v>
+        <v>49.67054334866313</v>
       </c>
       <c r="D6" t="n">
-        <v>35.05919226635785</v>
+        <v>33.00635781677777</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.21686843164731</v>
+        <v>15.69029180927252</v>
       </c>
       <c r="C7" t="n">
-        <v>54.97590794241288</v>
+        <v>33.53650157707104</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>25.78560345204247</v>
+        <v>23.03180114163017</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.20008090968388</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6283,7 +6283,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.252557060312999</v>
+        <v>7.290836157754213</v>
       </c>
       <c r="C21" t="n">
-        <v>75.24527950074736</v>
+        <v>76.55377965641924</v>
       </c>
       <c r="D21" t="n">
-        <v>5.439417795234749</v>
+        <v>6.379481638034936</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.870450360768427</v>
+        <v>8.175994880967437</v>
       </c>
       <c r="C2" t="n">
-        <v>5.680392216772045</v>
+        <v>9.231373663032759</v>
       </c>
       <c r="D2" t="n">
-        <v>32.12867536918112</v>
+        <v>27.9150142225538</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.9603134856694</v>
+        <v>26.22248118043231</v>
       </c>
       <c r="C3" t="n">
-        <v>26.35992585902686</v>
+        <v>15.52633994266331</v>
       </c>
       <c r="D3" t="n">
-        <v>80.74874867430016</v>
+        <v>63.60252501962961</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.5021404074224</v>
+        <v>48.11545498513618</v>
       </c>
       <c r="C4" t="n">
-        <v>76.06581212504287</v>
+        <v>36.30993884156828</v>
       </c>
       <c r="D4" t="n">
-        <v>98.46438599743385</v>
+        <v>71.1649275854428</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.11006322052944</v>
+        <v>49.13647259755287</v>
       </c>
       <c r="C5" t="n">
-        <v>108.6549271675158</v>
+        <v>56.79410469067799</v>
       </c>
       <c r="D5" t="n">
-        <v>65.55620295108078</v>
+        <v>48.10563750809372</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.61642405174254</v>
+        <v>41.78121879733577</v>
       </c>
       <c r="C6" t="n">
-        <v>129.4493252911675</v>
+        <v>66.49573550404497</v>
       </c>
       <c r="D6" t="n">
-        <v>42.18373535607696</v>
+        <v>37.15227837181205</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.55917958525995</v>
+        <v>27.42806736124739</v>
       </c>
       <c r="C7" t="n">
-        <v>99.53154575195012</v>
+        <v>55.27534099220816</v>
       </c>
       <c r="D7" t="n">
-        <v>35.87207936547421</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>12.35038611942487</v>
       </c>
       <c r="C8" t="n">
-        <v>50.65327280061418</v>
+        <v>35.29873870619407</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>28.28906009787183</v>
+        <v>26.73593522975338</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.451794827036013</v>
+        <v>7.506956407607358</v>
       </c>
       <c r="C21" t="n">
-        <v>83.83269180415515</v>
+        <v>86.32999868748462</v>
       </c>
       <c r="D21" t="n">
-        <v>6.52032047365651</v>
+        <v>7.506956407607358</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_78_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_78_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497630359506</v>
+        <v>10.84497604579684</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907184218376</v>
+        <v>37.78907094389177</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.550040756285473</v>
+        <v>1.570796326794897</v>
       </c>
       <c r="C2" t="n">
-        <v>4.62304993929823</v>
+        <v>4.925428232206248</v>
       </c>
       <c r="D2" t="n">
-        <v>25.78069471352124</v>
+        <v>12.48586730261093</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.20913762320035</v>
+        <v>10.02364406035993</v>
       </c>
       <c r="C3" t="n">
-        <v>27.23368131580652</v>
+        <v>55.23803457944679</v>
       </c>
       <c r="D3" t="n">
-        <v>70.67110849020665</v>
+        <v>61.19724314422493</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.83842220608933</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="C4" t="n">
-        <v>37.72660077879643</v>
+        <v>133.6129173048782</v>
       </c>
       <c r="D4" t="n">
-        <v>86.17388648796803</v>
+        <v>79.12886496229292</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.89290135590843</v>
+        <v>13.71992416684918</v>
       </c>
       <c r="C5" t="n">
-        <v>61.80101798233672</v>
+        <v>131.4805612912541</v>
       </c>
       <c r="D5" t="n">
-        <v>61.50649367106269</v>
+        <v>49.62734644967627</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.14476854754334</v>
+        <v>9.056622571676828</v>
       </c>
       <c r="C6" t="n">
-        <v>79.29576207201488</v>
+        <v>94.59139130418019</v>
       </c>
       <c r="D6" t="n">
-        <v>43.83405324691584</v>
+        <v>30.30949687321178</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.04606969330414</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>77.01418040734529</v>
+        <v>52.46067032413256</v>
       </c>
       <c r="D7" t="n">
-        <v>38.5669768136317</v>
+        <v>28.98511922018283</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.36283004441059</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>54.9091490985241</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>36.16562192904399</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>37.5813021185679</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>28.42257778564941</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.85539932116455</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.709945740792508</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>95.41057854230729</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.673688958391573</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.26809923871739</v>
+        <v>1.452004854581033</v>
       </c>
       <c r="C2" t="n">
-        <v>6.219371706403543</v>
+        <v>9.186213268637404</v>
       </c>
       <c r="D2" t="n">
-        <v>26.38643304704152</v>
+        <v>19.74098283699486</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.91599597025805</v>
+        <v>7.584001015306611</v>
       </c>
       <c r="C3" t="n">
-        <v>22.16295442337174</v>
+        <v>34.89131340893164</v>
       </c>
       <c r="D3" t="n">
-        <v>74.19067400993146</v>
+        <v>57.07390278638832</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.5403718146258</v>
+        <v>16.85955332503048</v>
       </c>
       <c r="C4" t="n">
-        <v>53.45027201001334</v>
+        <v>136.114410455299</v>
       </c>
       <c r="D4" t="n">
-        <v>100.4043194610256</v>
+        <v>91.30449999036186</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.47061097436206</v>
+        <v>17.30330328735004</v>
       </c>
       <c r="C5" t="n">
-        <v>65.06532909895736</v>
+        <v>193.8215405109266</v>
       </c>
       <c r="D5" t="n">
-        <v>76.03635969391547</v>
+        <v>65.82618356974865</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>68.91083485649213</v>
+        <v>13.52455637370406</v>
       </c>
       <c r="C6" t="n">
-        <v>88.83540451418115</v>
+        <v>152.594027418786</v>
       </c>
       <c r="D6" t="n">
-        <v>52.5284109157256</v>
+        <v>38.52083467153211</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>51.92169083450106</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>95.04005000502096</v>
+        <v>93.60277136600364</v>
       </c>
       <c r="D7" t="n">
-        <v>41.9206269713388</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.71045084717197</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>78.44164156932014</v>
+        <v>49.06775025825559</v>
       </c>
       <c r="D8" t="n">
-        <v>38.88702656521616</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.08749871886498</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>51.58593311964863</v>
+        <v>35.05624702324509</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>37.15424186722054</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>38.00836236991527</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>29.13827186204534</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.899291135949759</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104.6656075513343</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.874113919937198</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12.18152551429442</v>
+        <v>0.7932521450314228</v>
       </c>
       <c r="C2" t="n">
-        <v>5.16497467204247</v>
+        <v>4.042837046088365</v>
       </c>
       <c r="D2" t="n">
-        <v>32.53119192792231</v>
+        <v>13.47546898849172</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.69925071179776</v>
+        <v>7.220754364735291</v>
       </c>
       <c r="C3" t="n">
-        <v>23.00234871050277</v>
+        <v>37.66965941195011</v>
       </c>
       <c r="D3" t="n">
-        <v>76.71376560984577</v>
+        <v>60.60819452167684</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.99982974021331</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="C4" t="n">
-        <v>54.25432337979149</v>
+        <v>129.7841012583156</v>
       </c>
       <c r="D4" t="n">
-        <v>110.588970144882</v>
+        <v>98.93660664317656</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>71.56940763959248</v>
+        <v>17.30330328735004</v>
       </c>
       <c r="C5" t="n">
-        <v>79.74245727744719</v>
+        <v>236.4784782604505</v>
       </c>
       <c r="D5" t="n">
-        <v>91.6952355766521</v>
+        <v>73.90105843717866</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>78.57123226628075</v>
+        <v>10.74719211838983</v>
       </c>
       <c r="C6" t="n">
-        <v>94.83290123942491</v>
+        <v>191.8796435519264</v>
       </c>
       <c r="D6" t="n">
-        <v>61.70578845502478</v>
+        <v>38.84284791852506</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>65.27640485537042</v>
+        <v>4.132176087174825</v>
       </c>
       <c r="C7" t="n">
-        <v>110.9698882541297</v>
+        <v>87.85365680993432</v>
       </c>
       <c r="D7" t="n">
-        <v>46.77144237802229</v>
+        <v>32.75797564760332</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>42.72566008882119</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>99.80447161373074</v>
+        <v>42.14152020479433</v>
       </c>
       <c r="D8" t="n">
-        <v>40.72289477215769</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22.63124807829746</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>72.66405632982764</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>37.60780930658255</v>
+        <v>39.93749660876023</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.2494460323367</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>47.83074815090461</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.863979037466197</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>37.6716229073586</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>37.31623023842126</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>32.00006641992479</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>34.08137155292803</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.07399774625223</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113.0359684475312</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.10174690109681</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.96415836102838</v>
+        <v>0.7333655350723673</v>
       </c>
       <c r="C2" t="n">
-        <v>3.429244730934109</v>
+        <v>9.366854846218818</v>
       </c>
       <c r="D2" t="n">
-        <v>26.35305362509713</v>
+        <v>10.96023137021139</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>36.84990007890403</v>
+        <v>4.962734644967626</v>
       </c>
       <c r="C3" t="n">
-        <v>33.60522391636832</v>
+        <v>25.92795686915826</v>
       </c>
       <c r="D3" t="n">
-        <v>84.65610453720245</v>
+        <v>57.99183688985909</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.3827680981318</v>
+        <v>16.55324804130547</v>
       </c>
       <c r="C4" t="n">
-        <v>71.05006310404592</v>
+        <v>112.426801847232</v>
       </c>
       <c r="D4" t="n">
-        <v>105.7518992060579</v>
+        <v>105.4966448029537</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.25227776892498</v>
+        <v>22.13841073076558</v>
       </c>
       <c r="C5" t="n">
-        <v>56.64684253504097</v>
+        <v>239.9882263031328</v>
       </c>
       <c r="D5" t="n">
-        <v>62.39006660488482</v>
+        <v>89.51084693470295</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.53341746523807</v>
+        <v>15.93965572615122</v>
       </c>
       <c r="C6" t="n">
-        <v>73.05675541152641</v>
+        <v>278.4207036812827</v>
       </c>
       <c r="D6" t="n">
-        <v>30.79251674370121</v>
+        <v>50.15356321915257</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.32636651063322</v>
+        <v>7.186393195086651</v>
       </c>
       <c r="C7" t="n">
-        <v>70.18710687201296</v>
+        <v>172.7728697318749</v>
       </c>
       <c r="D7" t="n">
-        <v>28.62579956042849</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.68832831386403</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>53.49052366588747</v>
+        <v>73.60162538738336</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>36.49843440078366</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>40.71405904281946</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
         <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>20.58823110575986</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>47.22206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.658212930201868</v>
+        <v>0.3750276230222815</v>
       </c>
       <c r="C2" t="n">
-        <v>2.017491532227195</v>
+        <v>4.539601384437251</v>
       </c>
       <c r="D2" t="n">
-        <v>18.32039390894973</v>
+        <v>8.068984381204535</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>38.50905369908114</v>
+        <v>3.946625771072178</v>
       </c>
       <c r="C3" t="n">
-        <v>23.53740120931728</v>
+        <v>31.6711809390021</v>
       </c>
       <c r="D3" t="n">
-        <v>87.23810099937157</v>
+        <v>54.33482669153972</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.77010077741955</v>
+        <v>14.2049075327471</v>
       </c>
       <c r="C4" t="n">
-        <v>79.44793296617313</v>
+        <v>93.86980674155878</v>
       </c>
       <c r="D4" t="n">
-        <v>121.1054515527738</v>
+        <v>110.8314618278309</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.94641445355649</v>
+        <v>24.15099352447154</v>
       </c>
       <c r="C5" t="n">
-        <v>92.72607066611126</v>
+        <v>235.0549440892926</v>
       </c>
       <c r="D5" t="n">
-        <v>81.2150788338174</v>
+        <v>100.7027707631166</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.26802678992194</v>
+        <v>19.72331137831842</v>
       </c>
       <c r="C6" t="n">
-        <v>84.68948395914687</v>
+        <v>327.6082271594564</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>60.25672884355649</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.82920126165683</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>86.59603800079415</v>
+        <v>248.4096581101619</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.93452600345173</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>69.59609475405638</v>
+        <v>110.3189895262141</v>
       </c>
       <c r="D8" t="n">
-        <v>28.95664853675967</v>
+        <v>39.38771789438203</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>42.93280885441725</v>
+        <v>46.48280855297372</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>40.38124657107979</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>30.74146586308036</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.452446822937538</v>
+        <v>0.3926990816987241</v>
       </c>
       <c r="C2" t="n">
-        <v>5.072690387843269</v>
+        <v>13.69145348342602</v>
       </c>
       <c r="D2" t="n">
-        <v>18.07888397370501</v>
+        <v>9.443431167150068</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.35563901531138</v>
+        <v>2.66544501703009</v>
       </c>
       <c r="C3" t="n">
-        <v>14.75075925630833</v>
+        <v>24.64677611511618</v>
       </c>
       <c r="D3" t="n">
-        <v>81.86303231862028</v>
+        <v>48.97939296487337</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>63.04783756673017</v>
+        <v>11.18014285596268</v>
       </c>
       <c r="C4" t="n">
-        <v>69.0846042001438</v>
+        <v>86.70992073448679</v>
       </c>
       <c r="D4" t="n">
-        <v>135.6804779700219</v>
+        <v>112.1332592836622</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.70913460876503</v>
+        <v>23.09561474240622</v>
       </c>
       <c r="C5" t="n">
-        <v>120.1904626924158</v>
+        <v>208.8422803859028</v>
       </c>
       <c r="D5" t="n">
-        <v>103.4762080276138</v>
+        <v>113.8091026148115</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.76741757621409</v>
+        <v>24.79502001845745</v>
       </c>
       <c r="C6" t="n">
-        <v>116.3272854762046</v>
+        <v>348.056068343509</v>
       </c>
       <c r="D6" t="n">
-        <v>52.20639766873265</v>
+        <v>73.53977528201584</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.12402867256714</v>
+        <v>13.05528097107408</v>
       </c>
       <c r="C7" t="n">
-        <v>105.1608870881013</v>
+        <v>341.9525428662065</v>
       </c>
       <c r="D7" t="n">
-        <v>34.43480072645687</v>
+        <v>45.57371017884118</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.52696183746906</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>91.70996179221579</v>
+        <v>199.1082518982956</v>
       </c>
       <c r="D8" t="n">
-        <v>30.54217107911827</v>
+        <v>40.80634332701867</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.209374302911826</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>62.67968217763759</v>
+        <v>81.20624310447914</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.131775176547325</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
         <v>41.28249096357838</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47308888692249</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>30.56376952861169</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>29.50740899884213</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.03256190515617</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>33.32542582065798</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>39.67831521483909</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.367795536194059</v>
+        <v>0.2729258617806133</v>
       </c>
       <c r="C2" t="n">
-        <v>2.242311756499715</v>
+        <v>7.557493827291946</v>
       </c>
       <c r="D2" t="n">
-        <v>12.46328710541326</v>
+        <v>6.949791998363171</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.9643225919444</v>
+        <v>3.789546138392688</v>
       </c>
       <c r="C3" t="n">
-        <v>18.04943154257761</v>
+        <v>37.56166716448296</v>
       </c>
       <c r="D3" t="n">
-        <v>80.85183218324607</v>
+        <v>52.52350217720436</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>69.88865556992194</v>
+        <v>16.7446888436336</v>
       </c>
       <c r="C4" t="n">
-        <v>63.35414285045516</v>
+        <v>123.5558938225738</v>
       </c>
       <c r="D4" t="n">
-        <v>145.4694843290669</v>
+        <v>114.813430516256</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.38439710283758</v>
+        <v>14.79984664152067</v>
       </c>
       <c r="C5" t="n">
-        <v>140.119941088626</v>
+        <v>302.6237298340794</v>
       </c>
       <c r="D5" t="n">
-        <v>112.4591995214722</v>
+        <v>104.9979169691964</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.87180162803373</v>
+        <v>8.090582830697967</v>
       </c>
       <c r="C6" t="n">
-        <v>146.4757757259199</v>
+        <v>296.8559620716293</v>
       </c>
       <c r="D6" t="n">
-        <v>51.4818678629985</v>
+        <v>61.82654342264714</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.93550775115597</v>
+        <v>3.593196597543325</v>
       </c>
       <c r="C7" t="n">
-        <v>114.6828580715911</v>
+        <v>140.0148940842716</v>
       </c>
       <c r="D7" t="n">
-        <v>34.85400699617026</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>76.68922191723958</v>
+        <v>59.83261383532185</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
         <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>26.5140602485936</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>23.91537407545231</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>21.67895280517806</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>23.63361248433346</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.413356841216912</v>
+        <v>0.1570796326794897</v>
       </c>
       <c r="C2" t="n">
-        <v>3.365431130158066</v>
+        <v>3.702170592714722</v>
       </c>
       <c r="D2" t="n">
-        <v>13.46957850226624</v>
+        <v>5.600870652728053</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.81090790817464</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C3" t="n">
-        <v>13.06706194352505</v>
+        <v>33.32542582065798</v>
       </c>
       <c r="D3" t="n">
-        <v>73.39545836949155</v>
+        <v>46.4170314567892</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>65.71524607916875</v>
+        <v>11.43539725906685</v>
       </c>
       <c r="C4" t="n">
-        <v>54.4330014619644</v>
+        <v>105.1648140789183</v>
       </c>
       <c r="D4" t="n">
-        <v>151.6083527237222</v>
+        <v>110.103986778984</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>83.37492378316038</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="C5" t="n">
-        <v>129.9343086570654</v>
+        <v>240.012769995739</v>
       </c>
       <c r="D5" t="n">
-        <v>134.7203287152686</v>
+        <v>108.4831213192726</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.37498053642261</v>
+        <v>7.969827863075609</v>
       </c>
       <c r="C6" t="n">
-        <v>183.2657891948649</v>
+        <v>310.9440416275711</v>
       </c>
       <c r="D6" t="n">
-        <v>69.9171262533451</v>
+        <v>64.12088780747193</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.04500583014188</v>
+        <v>2.814670668075606</v>
       </c>
       <c r="C7" t="n">
-        <v>160.3763414703505</v>
+        <v>185.2891712133175</v>
       </c>
       <c r="D7" t="n">
-        <v>40.54323494228053</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>109.9017467519092</v>
+        <v>69.01195487002953</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>25.86905200690345</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>56.57812019574367</v>
+        <v>29.28749751309084</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>20.96718571959912</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>16.65534980254714</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.23287949455151</v>
+        <v>13.14952875068177</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.23654444346124</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>22.1305567491316</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>2.458296251434013</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.171445995344697</v>
+        <v>0.3563744166415922</v>
       </c>
       <c r="C2" t="n">
-        <v>2.269800692218626</v>
+        <v>6.705336820005715</v>
       </c>
       <c r="D2" t="n">
-        <v>10.2199936012093</v>
+        <v>13.37140373184156</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.24502031990098</v>
+        <v>1.413716694115407</v>
       </c>
       <c r="C3" t="n">
-        <v>13.35667751627786</v>
+        <v>22.54092728950677</v>
       </c>
       <c r="D3" t="n">
-        <v>68.50635480234243</v>
+        <v>40.79161711145497</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>58.65746183333842</v>
+        <v>8.040513697781378</v>
       </c>
       <c r="C4" t="n">
-        <v>45.49909735331843</v>
+        <v>94.20163746559419</v>
       </c>
       <c r="D4" t="n">
-        <v>154.0970831539879</v>
+        <v>107.5259173076319</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>92.38245896962486</v>
+        <v>16.14974973486003</v>
       </c>
       <c r="C5" t="n">
-        <v>122.2766765639403</v>
+        <v>216.1563007825415</v>
       </c>
       <c r="D5" t="n">
-        <v>152.7599427808037</v>
+        <v>123.0129873421254</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>79.49702035138549</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="C6" t="n">
-        <v>200.8960144677291</v>
+        <v>347.371790193649</v>
       </c>
       <c r="D6" t="n">
-        <v>85.61527204425161</v>
+        <v>81.79136473621028</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.22466566001905</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>202.1173086118121</v>
+        <v>317.4589193929529</v>
       </c>
       <c r="D7" t="n">
-        <v>45.51382356888213</v>
+        <v>42.63926629084747</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.759332943739289</v>
+        <v>1.835868206941535</v>
       </c>
       <c r="C8" t="n">
-        <v>142.5301317025519</v>
+        <v>153.0446496150353</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>28.53940576245478</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>69.0031191406913</v>
+        <v>55.24687030878498</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>22.74218556887735</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>20.21418523044183</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.05518316008284</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>13.0179745583127</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.202101158354601</v>
+        <v>0.3818998569520092</v>
       </c>
       <c r="C2" t="n">
-        <v>3.706097583531709</v>
+        <v>14.09200654675872</v>
       </c>
       <c r="D2" t="n">
-        <v>12.22864940409827</v>
+        <v>12.32093368829747</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.72545480017616</v>
+        <v>1.290998231084556</v>
       </c>
       <c r="C3" t="n">
-        <v>11.15265392024377</v>
+        <v>24.1755372170777</v>
       </c>
       <c r="D3" t="n">
-        <v>61.78138302825178</v>
+        <v>41.59174149041613</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.86394764639974</v>
+        <v>5.462444226429253</v>
       </c>
       <c r="C4" t="n">
-        <v>39.69205968269854</v>
+        <v>75.49148971805847</v>
       </c>
       <c r="D4" t="n">
-        <v>153.1015909818816</v>
+        <v>104.0161692649496</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>90.93438110586082</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="C5" t="n">
-        <v>104.7033926579224</v>
+        <v>193.7724531257142</v>
       </c>
       <c r="D5" t="n">
-        <v>168.7869740526329</v>
+        <v>132.1186972990145</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>98.25429198872504</v>
+        <v>17.38871533761951</v>
       </c>
       <c r="C6" t="n">
-        <v>198.9236833298972</v>
+        <v>347.1705319142784</v>
       </c>
       <c r="D6" t="n">
-        <v>106.6266364105418</v>
+        <v>97.16749728012383</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>53.53862930339555</v>
+        <v>10.24061030299848</v>
       </c>
       <c r="C7" t="n">
-        <v>240.8639452553209</v>
+        <v>403.2764314642793</v>
       </c>
       <c r="D7" t="n">
-        <v>55.45500082208532</v>
+        <v>53.77817574323178</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.85384276525424</v>
+        <v>3.588287859022091</v>
       </c>
       <c r="C8" t="n">
-        <v>197.0220380267711</v>
+        <v>272.0422888467912</v>
       </c>
       <c r="D8" t="n">
-        <v>38.63668090063322</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.549999698556465</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>112.0468654856884</v>
+        <v>112.7124904291678</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>24.51718541815559</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>51.67429041303087</v>
+        <v>42.27896488338889</v>
       </c>
       <c r="D10" t="n">
-        <v>27.18950266911542</v>
+        <v>21.06830573313655</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>17.17076734727672</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.210756961243575</v>
+        <v>2.09603134856694</v>
       </c>
       <c r="C2" t="n">
-        <v>5.316163818496478</v>
+        <v>14.84893402673301</v>
       </c>
       <c r="D2" t="n">
-        <v>6.567892141411161</v>
+        <v>11.56400620832318</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.988260085278044</v>
+        <v>0.8236863238630738</v>
       </c>
       <c r="C2" t="n">
-        <v>2.015528036818702</v>
+        <v>19.20887558129309</v>
       </c>
       <c r="D2" t="n">
-        <v>8.90150643440583</v>
+        <v>18.7140747383527</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.852943133008</v>
+        <v>1.266454538478385</v>
       </c>
       <c r="C3" t="n">
-        <v>13.95063487734718</v>
+        <v>37.7972866135022</v>
       </c>
       <c r="D3" t="n">
-        <v>67.1024555852695</v>
+        <v>41.32666961026948</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>69.11012964045422</v>
+        <v>4.045782289201106</v>
       </c>
       <c r="C4" t="n">
-        <v>57.15146085502382</v>
+        <v>68.57409539393547</v>
       </c>
       <c r="D4" t="n">
-        <v>158.3725944059827</v>
+        <v>101.4380997935974</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.54299826256906</v>
+        <v>11.87914722138641</v>
       </c>
       <c r="C5" t="n">
-        <v>162.8719441345459</v>
+        <v>168.2715565079033</v>
       </c>
       <c r="D5" t="n">
-        <v>154.3552828002048</v>
+        <v>135.9475133455771</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.24786775202249</v>
+        <v>18.31450342272425</v>
       </c>
       <c r="C6" t="n">
-        <v>203.4721204436727</v>
+        <v>332.5994324878472</v>
       </c>
       <c r="D6" t="n">
-        <v>84.68948395914687</v>
+        <v>111.9398549859256</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.82140403328509</v>
+        <v>14.13323995033708</v>
       </c>
       <c r="C7" t="n">
-        <v>138.5177288352952</v>
+        <v>442.4422743775015</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73423377625215</v>
+        <v>64.25833248606648</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.420008090968388</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>82.5306207575081</v>
+        <v>379.8578217271759</v>
       </c>
       <c r="D8" t="n">
-        <v>25.36836067773758</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>39.38280915586078</v>
+        <v>199.3546705720615</v>
       </c>
       <c r="D9" t="n">
-        <v>20.74531073843935</v>
+        <v>26.07031028627404</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>23.77302065833652</v>
+        <v>77.29790549387262</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>22.06477965294707</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.41424077792992</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>16.8811517745239</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>13.88583952886689</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.60978849752428</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.626036240139976</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.53116656572653</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>10.39179944945249</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.820602212030092</v>
+        <v>5.125704763872597</v>
       </c>
       <c r="C2" t="n">
-        <v>2.928553401768235</v>
+        <v>9.069385291832035</v>
       </c>
       <c r="D2" t="n">
-        <v>12.84322346695677</v>
+        <v>25.5008966178109</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.55150553007523</v>
+        <v>3.475386873033709</v>
       </c>
       <c r="C3" t="n">
-        <v>13.39594742444773</v>
+        <v>29.31498644880976</v>
       </c>
       <c r="D3" t="n">
-        <v>8.654106012935634</v>
+        <v>10.9121257327033</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39838064225535</v>
+        <v>11.67748375172508</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14446336239568</v>
+        <v>59.94441659218877</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576280075559453</v>
+        <v>0.7784989167816723</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.184609626127406</v>
+        <v>2.499529655012379</v>
       </c>
       <c r="C2" t="n">
-        <v>5.227806525114265</v>
+        <v>6.346017160251383</v>
       </c>
       <c r="D2" t="n">
-        <v>16.0800456478585</v>
+        <v>21.00351038465626</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.11172361630166</v>
+        <v>12.42892593576462</v>
       </c>
       <c r="C3" t="n">
-        <v>12.15894531709675</v>
+        <v>33.34506077474292</v>
       </c>
       <c r="D3" t="n">
-        <v>17.34748193404114</v>
+        <v>30.61089341841555</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.51343835378785</v>
+        <v>4.53076565509903</v>
       </c>
       <c r="C4" t="n">
-        <v>20.9436237746972</v>
+        <v>47.45179353706533</v>
       </c>
       <c r="D4" t="n">
-        <v>19.60353815840031</v>
+        <v>19.98641976305657</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.105088062083415</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44223371823817</v>
+        <v>13.62550488932273</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15140916490769</v>
+        <v>73.73802645986417</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250996572260668</v>
+        <v>1.603000575214439</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.571418221600648</v>
+        <v>1.638536918387927</v>
       </c>
       <c r="C2" t="n">
-        <v>3.425317740117121</v>
+        <v>4.939172700065703</v>
       </c>
       <c r="D2" t="n">
-        <v>24.35814229006761</v>
+        <v>21.17040749437822</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.63633674326795</v>
+        <v>10.28380720198534</v>
       </c>
       <c r="C3" t="n">
-        <v>17.12167996206437</v>
+        <v>27.90126975469435</v>
       </c>
       <c r="D3" t="n">
-        <v>26.18321127226244</v>
+        <v>40.85543071223102</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.14402347955058</v>
+        <v>15.96616291416588</v>
       </c>
       <c r="C4" t="n">
-        <v>26.54645792283375</v>
+        <v>69.81207924899068</v>
       </c>
       <c r="D4" t="n">
-        <v>23.89181213055038</v>
+        <v>31.38352886165779</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.21771131063132</v>
+        <v>4.884194828627883</v>
       </c>
       <c r="C5" t="n">
-        <v>24.29825568010856</v>
+        <v>54.60971604872884</v>
       </c>
       <c r="D5" t="n">
-        <v>29.50151851261666</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73816706119253</v>
+        <v>14.83107578394073</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1028190732744</v>
+        <v>87.33855739431763</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021450118357758</v>
+        <v>2.471845963990122</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.569675710370408</v>
+        <v>1.478512042595696</v>
       </c>
       <c r="C2" t="n">
-        <v>3.767947688899258</v>
+        <v>7.928594459497242</v>
       </c>
       <c r="D2" t="n">
-        <v>24.04201952930014</v>
+        <v>19.2383280124205</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.7920337176157</v>
+        <v>7.677267047210058</v>
       </c>
       <c r="C3" t="n">
-        <v>14.90293015046658</v>
+        <v>22.63419332141021</v>
       </c>
       <c r="D3" t="n">
-        <v>38.86739161113123</v>
+        <v>48.31180452598554</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.10948238345269</v>
+        <v>18.36555430334508</v>
       </c>
       <c r="C4" t="n">
-        <v>35.39102299039327</v>
+        <v>69.90141829007715</v>
       </c>
       <c r="D4" t="n">
-        <v>30.98788453684632</v>
+        <v>44.79714774478195</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.18369429834795</v>
+        <v>14.72621556370216</v>
       </c>
       <c r="C5" t="n">
-        <v>37.89546138392689</v>
+        <v>97.04576056479723</v>
       </c>
       <c r="D5" t="n">
-        <v>31.58773238414113</v>
+        <v>32.07860623626453</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.8994040702771</v>
+        <v>5.715735134124931</v>
       </c>
       <c r="C6" t="n">
-        <v>26.12332466230338</v>
+        <v>52.1258943569844</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>33.77113927838603</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.70215489718149</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>6.574764375340887</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06799916611409</v>
+        <v>16.06624889687261</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8721850360776</v>
+        <v>100.6254536172548</v>
       </c>
       <c r="D21" t="n">
-        <v>6.883047301376794</v>
+        <v>3.382368188815287</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.016370915802707</v>
+        <v>1.712167996206437</v>
       </c>
       <c r="C2" t="n">
-        <v>4.178318229274425</v>
+        <v>13.96830633602362</v>
       </c>
       <c r="D2" t="n">
-        <v>30.20248637344887</v>
+        <v>18.72683745850791</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.62437584436775</v>
+        <v>6.248824137530948</v>
       </c>
       <c r="C3" t="n">
-        <v>13.87700379952867</v>
+        <v>27.21895510024282</v>
       </c>
       <c r="D3" t="n">
-        <v>45.62181581634928</v>
+        <v>52.1847992192392</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.98864530037232</v>
+        <v>16.57877348161589</v>
       </c>
       <c r="C4" t="n">
-        <v>30.56671477172444</v>
+        <v>62.60114236129786</v>
       </c>
       <c r="D4" t="n">
-        <v>37.11399021134642</v>
+        <v>58.1724784674405</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.01064466049325</v>
+        <v>20.98485717827558</v>
       </c>
       <c r="C5" t="n">
-        <v>39.34353924769093</v>
+        <v>113.0973355292326</v>
       </c>
       <c r="D5" t="n">
-        <v>28.96155727528091</v>
+        <v>40.12893741108838</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.31450342272425</v>
+        <v>12.67927160034756</v>
       </c>
       <c r="C6" t="n">
-        <v>29.66547037922588</v>
+        <v>104.976318519703</v>
       </c>
       <c r="D6" t="n">
-        <v>30.47050349670826</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.886960145291375</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>19.10382857693868</v>
+        <v>46.95110220789945</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>22.2984356065578</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.064139247869128</v>
+        <v>17.32521136305809</v>
       </c>
       <c r="C21" t="n">
-        <v>66.22630544877308</v>
+        <v>114.3463949961834</v>
       </c>
       <c r="D21" t="n">
-        <v>5.298104435901846</v>
+        <v>4.331302840764522</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.077419199915256</v>
+        <v>3.636393496530185</v>
       </c>
       <c r="C2" t="n">
-        <v>3.991786165467531</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D2" t="n">
-        <v>21.19691468239288</v>
+        <v>22.26996492313464</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.33814748308418</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C3" t="n">
-        <v>15.49197877301467</v>
+        <v>41.59174149041613</v>
       </c>
       <c r="D3" t="n">
-        <v>60.73582172322892</v>
+        <v>54.5606286635165</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.50512670826415</v>
+        <v>14.14109393197106</v>
       </c>
       <c r="C4" t="n">
-        <v>33.31069960509428</v>
+        <v>65.37065263497811</v>
       </c>
       <c r="D4" t="n">
-        <v>53.19501760690918</v>
+        <v>69.78655380868027</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.23278168356029</v>
+        <v>23.0219836645877</v>
       </c>
       <c r="C5" t="n">
-        <v>49.70097752749479</v>
+        <v>114.2263453891164</v>
       </c>
       <c r="D5" t="n">
-        <v>36.61918936840603</v>
+        <v>50.60909415392309</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.59125846433062</v>
+        <v>19.84406634594078</v>
       </c>
       <c r="C6" t="n">
-        <v>49.67054334866313</v>
+        <v>139.9550074743126</v>
       </c>
       <c r="D6" t="n">
-        <v>33.00635781677777</v>
+        <v>40.17115256237099</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.69029180927252</v>
+        <v>10.71970318267092</v>
       </c>
       <c r="C7" t="n">
-        <v>33.53650157707104</v>
+        <v>97.19596796354696</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>23.03180114163017</v>
+        <v>42.80910864368217</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.290836157754213</v>
+        <v>17.71497065251967</v>
       </c>
       <c r="C21" t="n">
-        <v>76.55377965641924</v>
+        <v>127.5477886981416</v>
       </c>
       <c r="D21" t="n">
-        <v>6.379481638034936</v>
+        <v>5.314491195755901</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.175994880967437</v>
+        <v>3.112140222462389</v>
       </c>
       <c r="C2" t="n">
-        <v>9.231373663032759</v>
+        <v>11.67592544660732</v>
       </c>
       <c r="D2" t="n">
-        <v>27.9150142225538</v>
+        <v>17.66851343332985</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.22248118043231</v>
+        <v>8.70810213666921</v>
       </c>
       <c r="C3" t="n">
-        <v>15.52633994266331</v>
+        <v>64.13266877992288</v>
       </c>
       <c r="D3" t="n">
-        <v>63.60252501962961</v>
+        <v>60.83890523217485</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.11545498513618</v>
+        <v>11.05251565441059</v>
       </c>
       <c r="C4" t="n">
-        <v>36.30993884156828</v>
+        <v>97.17535126175778</v>
       </c>
       <c r="D4" t="n">
-        <v>71.1649275854428</v>
+        <v>64.57936398535519</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.13647259755287</v>
+        <v>11.16738013580747</v>
       </c>
       <c r="C5" t="n">
-        <v>56.79410469067799</v>
+        <v>83.62036070922208</v>
       </c>
       <c r="D5" t="n">
-        <v>48.10563750809372</v>
+        <v>38.55814108429348</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.78121879733577</v>
+        <v>6.641523219229673</v>
       </c>
       <c r="C6" t="n">
-        <v>66.49573550404497</v>
+        <v>64.00013283984957</v>
       </c>
       <c r="D6" t="n">
-        <v>37.15227837181205</v>
+        <v>25.96231803880691</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.42806736124739</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>55.27534099220816</v>
+        <v>30.06307819944583</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>26.82920126165683</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.35038611942487</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>35.29873870619407</v>
+        <v>23.03180114163017</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>26.73593522975338</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.61405964570653</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.83959354690535</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.506956407607358</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>86.32999868748462</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.506956407607358</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
